--- a/business/executors-desk/02-product/ledger/The-Estate-Ledger.xlsx
+++ b/business/executors-desk/02-product/ledger/The-Estate-Ledger.xlsx
@@ -122,13 +122,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -140,6 +142,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -611,7 +614,7 @@
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>1. Fill in the estate details below. Shaded cells are yours to type in; white cells hold formulas and update by themselves.</t>
@@ -619,7 +622,7 @@
       </c>
       <c r="B5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2. Inventory tab: one row per asset, at date-of-death value. Mark how each passes (A, B or C, the same sort as the notebook).</t>
@@ -627,7 +630,7 @@
       </c>
       <c r="B6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>3. Ledger tab: every transaction in the estate bank account, in date order. Money in on the left, money out on the right.</t>
@@ -635,7 +638,7 @@
       </c>
       <c r="B7" s="2" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>4. Tick the Receipt column for every outgoing amount. Rows without a receipt turn amber until you do.</t>
@@ -643,7 +646,7 @@
       </c>
       <c r="B8" s="2" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>5. Claims tab: every creditor claim as it arrives. Rows dated after the creditor window closes turn red.</t>
@@ -651,7 +654,7 @@
       </c>
       <c r="B9" s="2" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>6. Distribution tab: beneficiaries and their shares. The computed share updates from the ledger balance and your reserve.</t>
@@ -659,7 +662,7 @@
       </c>
       <c r="B10" s="2" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>7. Final accounting tab: print it. It pulls from the other tabs and is laid out the way courts and beneficiaries expect.</t>
@@ -667,7 +670,7 @@
       </c>
       <c r="B11" s="2" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>8. Delete the three gray italic example rows on each tab once you have entered your own.</t>
@@ -675,7 +678,7 @@
       </c>
       <c r="B12" s="2" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>9. Do not insert columns. Adding rows inside a table is fine; the totals cover 200 rows per table.</t>
@@ -683,7 +686,7 @@
       </c>
       <c r="B13" s="2" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>10. Categories are dropdowns. If a transaction fits none, use the closest and explain in Notes.</t>
@@ -691,7 +694,7 @@
       </c>
       <c r="B14" s="2" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>11. Reconcile the Ledger balance to the bank statement on the same day each month and write the date in the box below.</t>
@@ -699,7 +702,7 @@
       </c>
       <c r="B15" s="2" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>12. Nothing here is legal or tax advice. Your CPA will want the Final accounting tab and the Ledger tab; send both.</t>
@@ -805,31 +808,31 @@
           <t>Shaded cell</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Type here.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>White cell</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Formula. Leave it alone.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Gray italic row</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Example. Delete it.</t>
         </is>
@@ -982,23 +985,23 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <f>SUMIF($A$19:$A$218,A6,$E$19:$E$218)</f>
         <v/>
       </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>A: beneficiary designation (not probate)</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>SUMIF($D$19:$D$218,"A",$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1006,23 +1009,23 @@
       <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>brokerage</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <f>SUMIF($A$19:$A$218,A7,$E$19:$E$218)</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>B: joint / trust (not probate)</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>SUMIF($D$19:$D$218,"B",$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1030,23 +1033,23 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>retirement</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>SUMIF($A$19:$A$218,A8,$E$19:$E$218)</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>C: probate estate</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>SUMIF($D$19:$D$218,"C",$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1054,12 +1057,12 @@
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>life insurance</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="13">
         <f>SUMIF($A$19:$A$218,A9,$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1070,7 +1073,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>SUM($E$19:$E$218)</f>
         <v/>
       </c>
@@ -1078,23 +1081,23 @@
       <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>real estate</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <f>SUMIF($A$19:$A$218,A10,$E$19:$E$218)</f>
         <v/>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Assets not yet valued (count)</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="5">
+      <c r="F10" s="11">
         <f>SUMPRODUCT(($B$19:$B$218&lt;&gt;"")*($E$19:$E$218=""))</f>
         <v/>
       </c>
@@ -1102,12 +1105,12 @@
       <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>vehicle</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <f>SUMIF($A$19:$A$218,A11,$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1119,12 +1122,12 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>personal property</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <f>SUMIF($A$19:$A$218,A12,$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1136,12 +1139,12 @@
       <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <f>SUMIF($A$19:$A$218,A13,$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1153,12 +1156,12 @@
       <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>receivable</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>SUMIF($A$19:$A$218,A14,$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1170,12 +1173,12 @@
       <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>digital</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="13">
         <f>SUMIF($A$19:$A$218,A15,$E$19:$E$218)</f>
         <v/>
       </c>
@@ -1211,158 +1214,158 @@
       <c r="H17" s="2" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Institution / description</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Account last 4</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>Passes (A/B/C)</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Date-of-death value</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Source of value</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>First County Bank checking</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>4471</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>12480.22</v>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>statement</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>valued</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Sole name, no POD. Moved to estate account 2026-04-02.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>retirement</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Fidelity IRA</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>9902</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>86310</v>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>statement</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>Beneficiary: the three children equally. Not probate.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>real estate</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>14 Elm St, Dayton OH</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr"/>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr"/>
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>214000</v>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>appraisal</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>valued</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>Date-of-death appraisal 2026-04-10, J. Ortiz, licensed.</t>
         </is>
@@ -3430,12 +3433,12 @@
       <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Total money in</t>
         </is>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <f>SUM($D$13:$D$212)</f>
         <v/>
       </c>
@@ -3447,12 +3450,12 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Total money out</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <f>SUM($E$13:$E$212)</f>
         <v/>
       </c>
@@ -3469,7 +3472,7 @@
           <t>Balance in estate account</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <f>B5-B6</f>
         <v/>
       </c>
@@ -3481,12 +3484,12 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Outgoing rows without a receipt</t>
         </is>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="11">
         <f>COUNTIFS($E$13:$E$212,"&gt;0",$G$13:$G$212,"&lt;&gt;Yes")</f>
         <v/>
       </c>
@@ -3532,147 +3535,141 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Payee / payer</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Money in</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Money out</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Running balance</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Receipt?</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="A13" s="18" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>First County Bank (transfer of sole-name checking)</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>transfer in</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>12480.22</v>
       </c>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>IF(AND(D13="",E13=""),"",SUM($D$13:D13)-SUM($E$13:E13))</f>
         <v/>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Closing statement attached</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="A14" s="18" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Dayton Daily News</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>administration</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>145</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <f>IF(AND(D14="",E14=""),"",SUM($D$13:D14)-SUM($E$13:E14))</f>
         <v/>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>Notice to creditors, 3 runs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="A15" s="18" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Reimbursement to executor: death certificates</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>reimbursement to executor</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>187.5</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <f>IF(AND(D15="",E15=""),"",SUM($D$13:D15)-SUM($E$13:E15))</f>
         <v/>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Receipt in folder, not yet scanned</t>
         </is>
@@ -3684,7 +3681,7 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
-      <c r="F16" s="18">
+      <c r="F16" s="19">
         <f>IF(AND(D16="",E16=""),"",SUM($D$13:D16)-SUM($E$13:E16))</f>
         <v/>
       </c>
@@ -3697,7 +3694,7 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
-      <c r="F17" s="18">
+      <c r="F17" s="19">
         <f>IF(AND(D17="",E17=""),"",SUM($D$13:D17)-SUM($E$13:E17))</f>
         <v/>
       </c>
@@ -3710,7 +3707,7 @@
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="18">
+      <c r="F18" s="19">
         <f>IF(AND(D18="",E18=""),"",SUM($D$13:D18)-SUM($E$13:E18))</f>
         <v/>
       </c>
@@ -3723,7 +3720,7 @@
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
-      <c r="F19" s="18">
+      <c r="F19" s="19">
         <f>IF(AND(D19="",E19=""),"",SUM($D$13:D19)-SUM($E$13:E19))</f>
         <v/>
       </c>
@@ -3736,7 +3733,7 @@
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
-      <c r="F20" s="18">
+      <c r="F20" s="19">
         <f>IF(AND(D20="",E20=""),"",SUM($D$13:D20)-SUM($E$13:E20))</f>
         <v/>
       </c>
@@ -3749,7 +3746,7 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <f>IF(AND(D21="",E21=""),"",SUM($D$13:D21)-SUM($E$13:E21))</f>
         <v/>
       </c>
@@ -3762,7 +3759,7 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <f>IF(AND(D22="",E22=""),"",SUM($D$13:D22)-SUM($E$13:E22))</f>
         <v/>
       </c>
@@ -3775,7 +3772,7 @@
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <f>IF(AND(D23="",E23=""),"",SUM($D$13:D23)-SUM($E$13:E23))</f>
         <v/>
       </c>
@@ -3788,7 +3785,7 @@
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <f>IF(AND(D24="",E24=""),"",SUM($D$13:D24)-SUM($E$13:E24))</f>
         <v/>
       </c>
@@ -3801,7 +3798,7 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <f>IF(AND(D25="",E25=""),"",SUM($D$13:D25)-SUM($E$13:E25))</f>
         <v/>
       </c>
@@ -3814,7 +3811,7 @@
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="18">
+      <c r="F26" s="19">
         <f>IF(AND(D26="",E26=""),"",SUM($D$13:D26)-SUM($E$13:E26))</f>
         <v/>
       </c>
@@ -3827,7 +3824,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
-      <c r="F27" s="18">
+      <c r="F27" s="19">
         <f>IF(AND(D27="",E27=""),"",SUM($D$13:D27)-SUM($E$13:E27))</f>
         <v/>
       </c>
@@ -3840,7 +3837,7 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="18">
+      <c r="F28" s="19">
         <f>IF(AND(D28="",E28=""),"",SUM($D$13:D28)-SUM($E$13:E28))</f>
         <v/>
       </c>
@@ -3853,7 +3850,7 @@
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
-      <c r="F29" s="18">
+      <c r="F29" s="19">
         <f>IF(AND(D29="",E29=""),"",SUM($D$13:D29)-SUM($E$13:E29))</f>
         <v/>
       </c>
@@ -3866,7 +3863,7 @@
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="18">
+      <c r="F30" s="19">
         <f>IF(AND(D30="",E30=""),"",SUM($D$13:D30)-SUM($E$13:E30))</f>
         <v/>
       </c>
@@ -3879,7 +3876,7 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
-      <c r="F31" s="18">
+      <c r="F31" s="19">
         <f>IF(AND(D31="",E31=""),"",SUM($D$13:D31)-SUM($E$13:E31))</f>
         <v/>
       </c>
@@ -3892,7 +3889,7 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
-      <c r="F32" s="18">
+      <c r="F32" s="19">
         <f>IF(AND(D32="",E32=""),"",SUM($D$13:D32)-SUM($E$13:E32))</f>
         <v/>
       </c>
@@ -3905,7 +3902,7 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
-      <c r="F33" s="18">
+      <c r="F33" s="19">
         <f>IF(AND(D33="",E33=""),"",SUM($D$13:D33)-SUM($E$13:E33))</f>
         <v/>
       </c>
@@ -3918,7 +3915,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
-      <c r="F34" s="18">
+      <c r="F34" s="19">
         <f>IF(AND(D34="",E34=""),"",SUM($D$13:D34)-SUM($E$13:E34))</f>
         <v/>
       </c>
@@ -3931,7 +3928,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
-      <c r="F35" s="18">
+      <c r="F35" s="19">
         <f>IF(AND(D35="",E35=""),"",SUM($D$13:D35)-SUM($E$13:E35))</f>
         <v/>
       </c>
@@ -3944,7 +3941,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="18">
+      <c r="F36" s="19">
         <f>IF(AND(D36="",E36=""),"",SUM($D$13:D36)-SUM($E$13:E36))</f>
         <v/>
       </c>
@@ -3957,7 +3954,7 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
-      <c r="F37" s="18">
+      <c r="F37" s="19">
         <f>IF(AND(D37="",E37=""),"",SUM($D$13:D37)-SUM($E$13:E37))</f>
         <v/>
       </c>
@@ -3970,7 +3967,7 @@
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
-      <c r="F38" s="18">
+      <c r="F38" s="19">
         <f>IF(AND(D38="",E38=""),"",SUM($D$13:D38)-SUM($E$13:E38))</f>
         <v/>
       </c>
@@ -3983,7 +3980,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
-      <c r="F39" s="18">
+      <c r="F39" s="19">
         <f>IF(AND(D39="",E39=""),"",SUM($D$13:D39)-SUM($E$13:E39))</f>
         <v/>
       </c>
@@ -3996,7 +3993,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
-      <c r="F40" s="18">
+      <c r="F40" s="19">
         <f>IF(AND(D40="",E40=""),"",SUM($D$13:D40)-SUM($E$13:E40))</f>
         <v/>
       </c>
@@ -4009,7 +4006,7 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="9" t="n"/>
       <c r="E41" s="9" t="n"/>
-      <c r="F41" s="18">
+      <c r="F41" s="19">
         <f>IF(AND(D41="",E41=""),"",SUM($D$13:D41)-SUM($E$13:E41))</f>
         <v/>
       </c>
@@ -4022,7 +4019,7 @@
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <f>IF(AND(D42="",E42=""),"",SUM($D$13:D42)-SUM($E$13:E42))</f>
         <v/>
       </c>
@@ -4035,7 +4032,7 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
-      <c r="F43" s="18">
+      <c r="F43" s="19">
         <f>IF(AND(D43="",E43=""),"",SUM($D$13:D43)-SUM($E$13:E43))</f>
         <v/>
       </c>
@@ -4048,7 +4045,7 @@
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
-      <c r="F44" s="18">
+      <c r="F44" s="19">
         <f>IF(AND(D44="",E44=""),"",SUM($D$13:D44)-SUM($E$13:E44))</f>
         <v/>
       </c>
@@ -4061,7 +4058,7 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
-      <c r="F45" s="18">
+      <c r="F45" s="19">
         <f>IF(AND(D45="",E45=""),"",SUM($D$13:D45)-SUM($E$13:E45))</f>
         <v/>
       </c>
@@ -4074,7 +4071,7 @@
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="9" t="n"/>
-      <c r="F46" s="18">
+      <c r="F46" s="19">
         <f>IF(AND(D46="",E46=""),"",SUM($D$13:D46)-SUM($E$13:E46))</f>
         <v/>
       </c>
@@ -4087,7 +4084,7 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="9" t="n"/>
-      <c r="F47" s="18">
+      <c r="F47" s="19">
         <f>IF(AND(D47="",E47=""),"",SUM($D$13:D47)-SUM($E$13:E47))</f>
         <v/>
       </c>
@@ -4100,7 +4097,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="9" t="n"/>
-      <c r="F48" s="18">
+      <c r="F48" s="19">
         <f>IF(AND(D48="",E48=""),"",SUM($D$13:D48)-SUM($E$13:E48))</f>
         <v/>
       </c>
@@ -4113,7 +4110,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="9" t="n"/>
-      <c r="F49" s="18">
+      <c r="F49" s="19">
         <f>IF(AND(D49="",E49=""),"",SUM($D$13:D49)-SUM($E$13:E49))</f>
         <v/>
       </c>
@@ -4126,7 +4123,7 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="9" t="n"/>
       <c r="E50" s="9" t="n"/>
-      <c r="F50" s="18">
+      <c r="F50" s="19">
         <f>IF(AND(D50="",E50=""),"",SUM($D$13:D50)-SUM($E$13:E50))</f>
         <v/>
       </c>
@@ -4139,7 +4136,7 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="9" t="n"/>
       <c r="E51" s="9" t="n"/>
-      <c r="F51" s="18">
+      <c r="F51" s="19">
         <f>IF(AND(D51="",E51=""),"",SUM($D$13:D51)-SUM($E$13:E51))</f>
         <v/>
       </c>
@@ -4152,7 +4149,7 @@
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="9" t="n"/>
       <c r="E52" s="9" t="n"/>
-      <c r="F52" s="18">
+      <c r="F52" s="19">
         <f>IF(AND(D52="",E52=""),"",SUM($D$13:D52)-SUM($E$13:E52))</f>
         <v/>
       </c>
@@ -4165,7 +4162,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="9" t="n"/>
       <c r="E53" s="9" t="n"/>
-      <c r="F53" s="18">
+      <c r="F53" s="19">
         <f>IF(AND(D53="",E53=""),"",SUM($D$13:D53)-SUM($E$13:E53))</f>
         <v/>
       </c>
@@ -4178,7 +4175,7 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="9" t="n"/>
       <c r="E54" s="9" t="n"/>
-      <c r="F54" s="18">
+      <c r="F54" s="19">
         <f>IF(AND(D54="",E54=""),"",SUM($D$13:D54)-SUM($E$13:E54))</f>
         <v/>
       </c>
@@ -4191,7 +4188,7 @@
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="9" t="n"/>
       <c r="E55" s="9" t="n"/>
-      <c r="F55" s="18">
+      <c r="F55" s="19">
         <f>IF(AND(D55="",E55=""),"",SUM($D$13:D55)-SUM($E$13:E55))</f>
         <v/>
       </c>
@@ -4204,7 +4201,7 @@
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
-      <c r="F56" s="18">
+      <c r="F56" s="19">
         <f>IF(AND(D56="",E56=""),"",SUM($D$13:D56)-SUM($E$13:E56))</f>
         <v/>
       </c>
@@ -4217,7 +4214,7 @@
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="9" t="n"/>
       <c r="E57" s="9" t="n"/>
-      <c r="F57" s="18">
+      <c r="F57" s="19">
         <f>IF(AND(D57="",E57=""),"",SUM($D$13:D57)-SUM($E$13:E57))</f>
         <v/>
       </c>
@@ -4230,7 +4227,7 @@
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="9" t="n"/>
       <c r="E58" s="9" t="n"/>
-      <c r="F58" s="18">
+      <c r="F58" s="19">
         <f>IF(AND(D58="",E58=""),"",SUM($D$13:D58)-SUM($E$13:E58))</f>
         <v/>
       </c>
@@ -4243,7 +4240,7 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="9" t="n"/>
       <c r="E59" s="9" t="n"/>
-      <c r="F59" s="18">
+      <c r="F59" s="19">
         <f>IF(AND(D59="",E59=""),"",SUM($D$13:D59)-SUM($E$13:E59))</f>
         <v/>
       </c>
@@ -4256,7 +4253,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
-      <c r="F60" s="18">
+      <c r="F60" s="19">
         <f>IF(AND(D60="",E60=""),"",SUM($D$13:D60)-SUM($E$13:E60))</f>
         <v/>
       </c>
@@ -4269,7 +4266,7 @@
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="9" t="n"/>
       <c r="E61" s="9" t="n"/>
-      <c r="F61" s="18">
+      <c r="F61" s="19">
         <f>IF(AND(D61="",E61=""),"",SUM($D$13:D61)-SUM($E$13:E61))</f>
         <v/>
       </c>
@@ -4282,7 +4279,7 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="9" t="n"/>
       <c r="E62" s="9" t="n"/>
-      <c r="F62" s="18">
+      <c r="F62" s="19">
         <f>IF(AND(D62="",E62=""),"",SUM($D$13:D62)-SUM($E$13:E62))</f>
         <v/>
       </c>
@@ -4295,7 +4292,7 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="9" t="n"/>
       <c r="E63" s="9" t="n"/>
-      <c r="F63" s="18">
+      <c r="F63" s="19">
         <f>IF(AND(D63="",E63=""),"",SUM($D$13:D63)-SUM($E$13:E63))</f>
         <v/>
       </c>
@@ -4308,7 +4305,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="9" t="n"/>
       <c r="E64" s="9" t="n"/>
-      <c r="F64" s="18">
+      <c r="F64" s="19">
         <f>IF(AND(D64="",E64=""),"",SUM($D$13:D64)-SUM($E$13:E64))</f>
         <v/>
       </c>
@@ -4321,7 +4318,7 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="9" t="n"/>
       <c r="E65" s="9" t="n"/>
-      <c r="F65" s="18">
+      <c r="F65" s="19">
         <f>IF(AND(D65="",E65=""),"",SUM($D$13:D65)-SUM($E$13:E65))</f>
         <v/>
       </c>
@@ -4334,7 +4331,7 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="9" t="n"/>
       <c r="E66" s="9" t="n"/>
-      <c r="F66" s="18">
+      <c r="F66" s="19">
         <f>IF(AND(D66="",E66=""),"",SUM($D$13:D66)-SUM($E$13:E66))</f>
         <v/>
       </c>
@@ -4347,7 +4344,7 @@
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="9" t="n"/>
       <c r="E67" s="9" t="n"/>
-      <c r="F67" s="18">
+      <c r="F67" s="19">
         <f>IF(AND(D67="",E67=""),"",SUM($D$13:D67)-SUM($E$13:E67))</f>
         <v/>
       </c>
@@ -4360,7 +4357,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="9" t="n"/>
       <c r="E68" s="9" t="n"/>
-      <c r="F68" s="18">
+      <c r="F68" s="19">
         <f>IF(AND(D68="",E68=""),"",SUM($D$13:D68)-SUM($E$13:E68))</f>
         <v/>
       </c>
@@ -4373,7 +4370,7 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="9" t="n"/>
       <c r="E69" s="9" t="n"/>
-      <c r="F69" s="18">
+      <c r="F69" s="19">
         <f>IF(AND(D69="",E69=""),"",SUM($D$13:D69)-SUM($E$13:E69))</f>
         <v/>
       </c>
@@ -4386,7 +4383,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="9" t="n"/>
       <c r="E70" s="9" t="n"/>
-      <c r="F70" s="18">
+      <c r="F70" s="19">
         <f>IF(AND(D70="",E70=""),"",SUM($D$13:D70)-SUM($E$13:E70))</f>
         <v/>
       </c>
@@ -4399,7 +4396,7 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="9" t="n"/>
       <c r="E71" s="9" t="n"/>
-      <c r="F71" s="18">
+      <c r="F71" s="19">
         <f>IF(AND(D71="",E71=""),"",SUM($D$13:D71)-SUM($E$13:E71))</f>
         <v/>
       </c>
@@ -4412,7 +4409,7 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="9" t="n"/>
       <c r="E72" s="9" t="n"/>
-      <c r="F72" s="18">
+      <c r="F72" s="19">
         <f>IF(AND(D72="",E72=""),"",SUM($D$13:D72)-SUM($E$13:E72))</f>
         <v/>
       </c>
@@ -4425,7 +4422,7 @@
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="9" t="n"/>
       <c r="E73" s="9" t="n"/>
-      <c r="F73" s="18">
+      <c r="F73" s="19">
         <f>IF(AND(D73="",E73=""),"",SUM($D$13:D73)-SUM($E$13:E73))</f>
         <v/>
       </c>
@@ -4438,7 +4435,7 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="9" t="n"/>
       <c r="E74" s="9" t="n"/>
-      <c r="F74" s="18">
+      <c r="F74" s="19">
         <f>IF(AND(D74="",E74=""),"",SUM($D$13:D74)-SUM($E$13:E74))</f>
         <v/>
       </c>
@@ -4451,7 +4448,7 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="9" t="n"/>
-      <c r="F75" s="18">
+      <c r="F75" s="19">
         <f>IF(AND(D75="",E75=""),"",SUM($D$13:D75)-SUM($E$13:E75))</f>
         <v/>
       </c>
@@ -4464,7 +4461,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="9" t="n"/>
       <c r="E76" s="9" t="n"/>
-      <c r="F76" s="18">
+      <c r="F76" s="19">
         <f>IF(AND(D76="",E76=""),"",SUM($D$13:D76)-SUM($E$13:E76))</f>
         <v/>
       </c>
@@ -4477,7 +4474,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="9" t="n"/>
       <c r="E77" s="9" t="n"/>
-      <c r="F77" s="18">
+      <c r="F77" s="19">
         <f>IF(AND(D77="",E77=""),"",SUM($D$13:D77)-SUM($E$13:E77))</f>
         <v/>
       </c>
@@ -4490,7 +4487,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="9" t="n"/>
       <c r="E78" s="9" t="n"/>
-      <c r="F78" s="18">
+      <c r="F78" s="19">
         <f>IF(AND(D78="",E78=""),"",SUM($D$13:D78)-SUM($E$13:E78))</f>
         <v/>
       </c>
@@ -4503,7 +4500,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="9" t="n"/>
       <c r="E79" s="9" t="n"/>
-      <c r="F79" s="18">
+      <c r="F79" s="19">
         <f>IF(AND(D79="",E79=""),"",SUM($D$13:D79)-SUM($E$13:E79))</f>
         <v/>
       </c>
@@ -4516,7 +4513,7 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="9" t="n"/>
       <c r="E80" s="9" t="n"/>
-      <c r="F80" s="18">
+      <c r="F80" s="19">
         <f>IF(AND(D80="",E80=""),"",SUM($D$13:D80)-SUM($E$13:E80))</f>
         <v/>
       </c>
@@ -4529,7 +4526,7 @@
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="9" t="n"/>
       <c r="E81" s="9" t="n"/>
-      <c r="F81" s="18">
+      <c r="F81" s="19">
         <f>IF(AND(D81="",E81=""),"",SUM($D$13:D81)-SUM($E$13:E81))</f>
         <v/>
       </c>
@@ -4542,7 +4539,7 @@
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="9" t="n"/>
       <c r="E82" s="9" t="n"/>
-      <c r="F82" s="18">
+      <c r="F82" s="19">
         <f>IF(AND(D82="",E82=""),"",SUM($D$13:D82)-SUM($E$13:E82))</f>
         <v/>
       </c>
@@ -4555,7 +4552,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="9" t="n"/>
       <c r="E83" s="9" t="n"/>
-      <c r="F83" s="18">
+      <c r="F83" s="19">
         <f>IF(AND(D83="",E83=""),"",SUM($D$13:D83)-SUM($E$13:E83))</f>
         <v/>
       </c>
@@ -4568,7 +4565,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="9" t="n"/>
       <c r="E84" s="9" t="n"/>
-      <c r="F84" s="18">
+      <c r="F84" s="19">
         <f>IF(AND(D84="",E84=""),"",SUM($D$13:D84)-SUM($E$13:E84))</f>
         <v/>
       </c>
@@ -4581,7 +4578,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="9" t="n"/>
       <c r="E85" s="9" t="n"/>
-      <c r="F85" s="18">
+      <c r="F85" s="19">
         <f>IF(AND(D85="",E85=""),"",SUM($D$13:D85)-SUM($E$13:E85))</f>
         <v/>
       </c>
@@ -4594,7 +4591,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="9" t="n"/>
       <c r="E86" s="9" t="n"/>
-      <c r="F86" s="18">
+      <c r="F86" s="19">
         <f>IF(AND(D86="",E86=""),"",SUM($D$13:D86)-SUM($E$13:E86))</f>
         <v/>
       </c>
@@ -4607,7 +4604,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="9" t="n"/>
-      <c r="F87" s="18">
+      <c r="F87" s="19">
         <f>IF(AND(D87="",E87=""),"",SUM($D$13:D87)-SUM($E$13:E87))</f>
         <v/>
       </c>
@@ -4620,7 +4617,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="9" t="n"/>
       <c r="E88" s="9" t="n"/>
-      <c r="F88" s="18">
+      <c r="F88" s="19">
         <f>IF(AND(D88="",E88=""),"",SUM($D$13:D88)-SUM($E$13:E88))</f>
         <v/>
       </c>
@@ -4633,7 +4630,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="9" t="n"/>
       <c r="E89" s="9" t="n"/>
-      <c r="F89" s="18">
+      <c r="F89" s="19">
         <f>IF(AND(D89="",E89=""),"",SUM($D$13:D89)-SUM($E$13:E89))</f>
         <v/>
       </c>
@@ -4646,7 +4643,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="9" t="n"/>
       <c r="E90" s="9" t="n"/>
-      <c r="F90" s="18">
+      <c r="F90" s="19">
         <f>IF(AND(D90="",E90=""),"",SUM($D$13:D90)-SUM($E$13:E90))</f>
         <v/>
       </c>
@@ -4659,7 +4656,7 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="9" t="n"/>
       <c r="E91" s="9" t="n"/>
-      <c r="F91" s="18">
+      <c r="F91" s="19">
         <f>IF(AND(D91="",E91=""),"",SUM($D$13:D91)-SUM($E$13:E91))</f>
         <v/>
       </c>
@@ -4672,7 +4669,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="9" t="n"/>
       <c r="E92" s="9" t="n"/>
-      <c r="F92" s="18">
+      <c r="F92" s="19">
         <f>IF(AND(D92="",E92=""),"",SUM($D$13:D92)-SUM($E$13:E92))</f>
         <v/>
       </c>
@@ -4685,7 +4682,7 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="9" t="n"/>
       <c r="E93" s="9" t="n"/>
-      <c r="F93" s="18">
+      <c r="F93" s="19">
         <f>IF(AND(D93="",E93=""),"",SUM($D$13:D93)-SUM($E$13:E93))</f>
         <v/>
       </c>
@@ -4698,7 +4695,7 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="9" t="n"/>
       <c r="E94" s="9" t="n"/>
-      <c r="F94" s="18">
+      <c r="F94" s="19">
         <f>IF(AND(D94="",E94=""),"",SUM($D$13:D94)-SUM($E$13:E94))</f>
         <v/>
       </c>
@@ -4711,7 +4708,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="9" t="n"/>
       <c r="E95" s="9" t="n"/>
-      <c r="F95" s="18">
+      <c r="F95" s="19">
         <f>IF(AND(D95="",E95=""),"",SUM($D$13:D95)-SUM($E$13:E95))</f>
         <v/>
       </c>
@@ -4724,7 +4721,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="9" t="n"/>
       <c r="E96" s="9" t="n"/>
-      <c r="F96" s="18">
+      <c r="F96" s="19">
         <f>IF(AND(D96="",E96=""),"",SUM($D$13:D96)-SUM($E$13:E96))</f>
         <v/>
       </c>
@@ -4737,7 +4734,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="9" t="n"/>
       <c r="E97" s="9" t="n"/>
-      <c r="F97" s="18">
+      <c r="F97" s="19">
         <f>IF(AND(D97="",E97=""),"",SUM($D$13:D97)-SUM($E$13:E97))</f>
         <v/>
       </c>
@@ -4750,7 +4747,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="9" t="n"/>
       <c r="E98" s="9" t="n"/>
-      <c r="F98" s="18">
+      <c r="F98" s="19">
         <f>IF(AND(D98="",E98=""),"",SUM($D$13:D98)-SUM($E$13:E98))</f>
         <v/>
       </c>
@@ -4763,7 +4760,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="9" t="n"/>
       <c r="E99" s="9" t="n"/>
-      <c r="F99" s="18">
+      <c r="F99" s="19">
         <f>IF(AND(D99="",E99=""),"",SUM($D$13:D99)-SUM($E$13:E99))</f>
         <v/>
       </c>
@@ -4776,7 +4773,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="9" t="n"/>
       <c r="E100" s="9" t="n"/>
-      <c r="F100" s="18">
+      <c r="F100" s="19">
         <f>IF(AND(D100="",E100=""),"",SUM($D$13:D100)-SUM($E$13:E100))</f>
         <v/>
       </c>
@@ -4789,7 +4786,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="9" t="n"/>
       <c r="E101" s="9" t="n"/>
-      <c r="F101" s="18">
+      <c r="F101" s="19">
         <f>IF(AND(D101="",E101=""),"",SUM($D$13:D101)-SUM($E$13:E101))</f>
         <v/>
       </c>
@@ -4802,7 +4799,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="9" t="n"/>
       <c r="E102" s="9" t="n"/>
-      <c r="F102" s="18">
+      <c r="F102" s="19">
         <f>IF(AND(D102="",E102=""),"",SUM($D$13:D102)-SUM($E$13:E102))</f>
         <v/>
       </c>
@@ -4815,7 +4812,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="9" t="n"/>
       <c r="E103" s="9" t="n"/>
-      <c r="F103" s="18">
+      <c r="F103" s="19">
         <f>IF(AND(D103="",E103=""),"",SUM($D$13:D103)-SUM($E$13:E103))</f>
         <v/>
       </c>
@@ -4828,7 +4825,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="9" t="n"/>
       <c r="E104" s="9" t="n"/>
-      <c r="F104" s="18">
+      <c r="F104" s="19">
         <f>IF(AND(D104="",E104=""),"",SUM($D$13:D104)-SUM($E$13:E104))</f>
         <v/>
       </c>
@@ -4841,7 +4838,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="9" t="n"/>
       <c r="E105" s="9" t="n"/>
-      <c r="F105" s="18">
+      <c r="F105" s="19">
         <f>IF(AND(D105="",E105=""),"",SUM($D$13:D105)-SUM($E$13:E105))</f>
         <v/>
       </c>
@@ -4854,7 +4851,7 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="9" t="n"/>
       <c r="E106" s="9" t="n"/>
-      <c r="F106" s="18">
+      <c r="F106" s="19">
         <f>IF(AND(D106="",E106=""),"",SUM($D$13:D106)-SUM($E$13:E106))</f>
         <v/>
       </c>
@@ -4867,7 +4864,7 @@
       <c r="C107" s="7" t="n"/>
       <c r="D107" s="9" t="n"/>
       <c r="E107" s="9" t="n"/>
-      <c r="F107" s="18">
+      <c r="F107" s="19">
         <f>IF(AND(D107="",E107=""),"",SUM($D$13:D107)-SUM($E$13:E107))</f>
         <v/>
       </c>
@@ -4880,7 +4877,7 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="9" t="n"/>
       <c r="E108" s="9" t="n"/>
-      <c r="F108" s="18">
+      <c r="F108" s="19">
         <f>IF(AND(D108="",E108=""),"",SUM($D$13:D108)-SUM($E$13:E108))</f>
         <v/>
       </c>
@@ -4893,7 +4890,7 @@
       <c r="C109" s="7" t="n"/>
       <c r="D109" s="9" t="n"/>
       <c r="E109" s="9" t="n"/>
-      <c r="F109" s="18">
+      <c r="F109" s="19">
         <f>IF(AND(D109="",E109=""),"",SUM($D$13:D109)-SUM($E$13:E109))</f>
         <v/>
       </c>
@@ -4906,7 +4903,7 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="9" t="n"/>
       <c r="E110" s="9" t="n"/>
-      <c r="F110" s="18">
+      <c r="F110" s="19">
         <f>IF(AND(D110="",E110=""),"",SUM($D$13:D110)-SUM($E$13:E110))</f>
         <v/>
       </c>
@@ -4919,7 +4916,7 @@
       <c r="C111" s="7" t="n"/>
       <c r="D111" s="9" t="n"/>
       <c r="E111" s="9" t="n"/>
-      <c r="F111" s="18">
+      <c r="F111" s="19">
         <f>IF(AND(D111="",E111=""),"",SUM($D$13:D111)-SUM($E$13:E111))</f>
         <v/>
       </c>
@@ -4932,7 +4929,7 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="9" t="n"/>
       <c r="E112" s="9" t="n"/>
-      <c r="F112" s="18">
+      <c r="F112" s="19">
         <f>IF(AND(D112="",E112=""),"",SUM($D$13:D112)-SUM($E$13:E112))</f>
         <v/>
       </c>
@@ -4945,7 +4942,7 @@
       <c r="C113" s="7" t="n"/>
       <c r="D113" s="9" t="n"/>
       <c r="E113" s="9" t="n"/>
-      <c r="F113" s="18">
+      <c r="F113" s="19">
         <f>IF(AND(D113="",E113=""),"",SUM($D$13:D113)-SUM($E$13:E113))</f>
         <v/>
       </c>
@@ -4958,7 +4955,7 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="9" t="n"/>
       <c r="E114" s="9" t="n"/>
-      <c r="F114" s="18">
+      <c r="F114" s="19">
         <f>IF(AND(D114="",E114=""),"",SUM($D$13:D114)-SUM($E$13:E114))</f>
         <v/>
       </c>
@@ -4971,7 +4968,7 @@
       <c r="C115" s="7" t="n"/>
       <c r="D115" s="9" t="n"/>
       <c r="E115" s="9" t="n"/>
-      <c r="F115" s="18">
+      <c r="F115" s="19">
         <f>IF(AND(D115="",E115=""),"",SUM($D$13:D115)-SUM($E$13:E115))</f>
         <v/>
       </c>
@@ -4984,7 +4981,7 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="9" t="n"/>
       <c r="E116" s="9" t="n"/>
-      <c r="F116" s="18">
+      <c r="F116" s="19">
         <f>IF(AND(D116="",E116=""),"",SUM($D$13:D116)-SUM($E$13:E116))</f>
         <v/>
       </c>
@@ -4997,7 +4994,7 @@
       <c r="C117" s="7" t="n"/>
       <c r="D117" s="9" t="n"/>
       <c r="E117" s="9" t="n"/>
-      <c r="F117" s="18">
+      <c r="F117" s="19">
         <f>IF(AND(D117="",E117=""),"",SUM($D$13:D117)-SUM($E$13:E117))</f>
         <v/>
       </c>
@@ -5010,7 +5007,7 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="9" t="n"/>
       <c r="E118" s="9" t="n"/>
-      <c r="F118" s="18">
+      <c r="F118" s="19">
         <f>IF(AND(D118="",E118=""),"",SUM($D$13:D118)-SUM($E$13:E118))</f>
         <v/>
       </c>
@@ -5023,7 +5020,7 @@
       <c r="C119" s="7" t="n"/>
       <c r="D119" s="9" t="n"/>
       <c r="E119" s="9" t="n"/>
-      <c r="F119" s="18">
+      <c r="F119" s="19">
         <f>IF(AND(D119="",E119=""),"",SUM($D$13:D119)-SUM($E$13:E119))</f>
         <v/>
       </c>
@@ -5036,7 +5033,7 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="9" t="n"/>
       <c r="E120" s="9" t="n"/>
-      <c r="F120" s="18">
+      <c r="F120" s="19">
         <f>IF(AND(D120="",E120=""),"",SUM($D$13:D120)-SUM($E$13:E120))</f>
         <v/>
       </c>
@@ -5049,7 +5046,7 @@
       <c r="C121" s="7" t="n"/>
       <c r="D121" s="9" t="n"/>
       <c r="E121" s="9" t="n"/>
-      <c r="F121" s="18">
+      <c r="F121" s="19">
         <f>IF(AND(D121="",E121=""),"",SUM($D$13:D121)-SUM($E$13:E121))</f>
         <v/>
       </c>
@@ -5062,7 +5059,7 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="9" t="n"/>
       <c r="E122" s="9" t="n"/>
-      <c r="F122" s="18">
+      <c r="F122" s="19">
         <f>IF(AND(D122="",E122=""),"",SUM($D$13:D122)-SUM($E$13:E122))</f>
         <v/>
       </c>
@@ -5075,7 +5072,7 @@
       <c r="C123" s="7" t="n"/>
       <c r="D123" s="9" t="n"/>
       <c r="E123" s="9" t="n"/>
-      <c r="F123" s="18">
+      <c r="F123" s="19">
         <f>IF(AND(D123="",E123=""),"",SUM($D$13:D123)-SUM($E$13:E123))</f>
         <v/>
       </c>
@@ -5088,7 +5085,7 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="9" t="n"/>
       <c r="E124" s="9" t="n"/>
-      <c r="F124" s="18">
+      <c r="F124" s="19">
         <f>IF(AND(D124="",E124=""),"",SUM($D$13:D124)-SUM($E$13:E124))</f>
         <v/>
       </c>
@@ -5101,7 +5098,7 @@
       <c r="C125" s="7" t="n"/>
       <c r="D125" s="9" t="n"/>
       <c r="E125" s="9" t="n"/>
-      <c r="F125" s="18">
+      <c r="F125" s="19">
         <f>IF(AND(D125="",E125=""),"",SUM($D$13:D125)-SUM($E$13:E125))</f>
         <v/>
       </c>
@@ -5114,7 +5111,7 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="9" t="n"/>
       <c r="E126" s="9" t="n"/>
-      <c r="F126" s="18">
+      <c r="F126" s="19">
         <f>IF(AND(D126="",E126=""),"",SUM($D$13:D126)-SUM($E$13:E126))</f>
         <v/>
       </c>
@@ -5127,7 +5124,7 @@
       <c r="C127" s="7" t="n"/>
       <c r="D127" s="9" t="n"/>
       <c r="E127" s="9" t="n"/>
-      <c r="F127" s="18">
+      <c r="F127" s="19">
         <f>IF(AND(D127="",E127=""),"",SUM($D$13:D127)-SUM($E$13:E127))</f>
         <v/>
       </c>
@@ -5140,7 +5137,7 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="9" t="n"/>
       <c r="E128" s="9" t="n"/>
-      <c r="F128" s="18">
+      <c r="F128" s="19">
         <f>IF(AND(D128="",E128=""),"",SUM($D$13:D128)-SUM($E$13:E128))</f>
         <v/>
       </c>
@@ -5153,7 +5150,7 @@
       <c r="C129" s="7" t="n"/>
       <c r="D129" s="9" t="n"/>
       <c r="E129" s="9" t="n"/>
-      <c r="F129" s="18">
+      <c r="F129" s="19">
         <f>IF(AND(D129="",E129=""),"",SUM($D$13:D129)-SUM($E$13:E129))</f>
         <v/>
       </c>
@@ -5166,7 +5163,7 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="9" t="n"/>
       <c r="E130" s="9" t="n"/>
-      <c r="F130" s="18">
+      <c r="F130" s="19">
         <f>IF(AND(D130="",E130=""),"",SUM($D$13:D130)-SUM($E$13:E130))</f>
         <v/>
       </c>
@@ -5179,7 +5176,7 @@
       <c r="C131" s="7" t="n"/>
       <c r="D131" s="9" t="n"/>
       <c r="E131" s="9" t="n"/>
-      <c r="F131" s="18">
+      <c r="F131" s="19">
         <f>IF(AND(D131="",E131=""),"",SUM($D$13:D131)-SUM($E$13:E131))</f>
         <v/>
       </c>
@@ -5192,7 +5189,7 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="9" t="n"/>
       <c r="E132" s="9" t="n"/>
-      <c r="F132" s="18">
+      <c r="F132" s="19">
         <f>IF(AND(D132="",E132=""),"",SUM($D$13:D132)-SUM($E$13:E132))</f>
         <v/>
       </c>
@@ -5205,7 +5202,7 @@
       <c r="C133" s="7" t="n"/>
       <c r="D133" s="9" t="n"/>
       <c r="E133" s="9" t="n"/>
-      <c r="F133" s="18">
+      <c r="F133" s="19">
         <f>IF(AND(D133="",E133=""),"",SUM($D$13:D133)-SUM($E$13:E133))</f>
         <v/>
       </c>
@@ -5218,7 +5215,7 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="9" t="n"/>
       <c r="E134" s="9" t="n"/>
-      <c r="F134" s="18">
+      <c r="F134" s="19">
         <f>IF(AND(D134="",E134=""),"",SUM($D$13:D134)-SUM($E$13:E134))</f>
         <v/>
       </c>
@@ -5231,7 +5228,7 @@
       <c r="C135" s="7" t="n"/>
       <c r="D135" s="9" t="n"/>
       <c r="E135" s="9" t="n"/>
-      <c r="F135" s="18">
+      <c r="F135" s="19">
         <f>IF(AND(D135="",E135=""),"",SUM($D$13:D135)-SUM($E$13:E135))</f>
         <v/>
       </c>
@@ -5244,7 +5241,7 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="9" t="n"/>
       <c r="E136" s="9" t="n"/>
-      <c r="F136" s="18">
+      <c r="F136" s="19">
         <f>IF(AND(D136="",E136=""),"",SUM($D$13:D136)-SUM($E$13:E136))</f>
         <v/>
       </c>
@@ -5257,7 +5254,7 @@
       <c r="C137" s="7" t="n"/>
       <c r="D137" s="9" t="n"/>
       <c r="E137" s="9" t="n"/>
-      <c r="F137" s="18">
+      <c r="F137" s="19">
         <f>IF(AND(D137="",E137=""),"",SUM($D$13:D137)-SUM($E$13:E137))</f>
         <v/>
       </c>
@@ -5270,7 +5267,7 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="9" t="n"/>
       <c r="E138" s="9" t="n"/>
-      <c r="F138" s="18">
+      <c r="F138" s="19">
         <f>IF(AND(D138="",E138=""),"",SUM($D$13:D138)-SUM($E$13:E138))</f>
         <v/>
       </c>
@@ -5283,7 +5280,7 @@
       <c r="C139" s="7" t="n"/>
       <c r="D139" s="9" t="n"/>
       <c r="E139" s="9" t="n"/>
-      <c r="F139" s="18">
+      <c r="F139" s="19">
         <f>IF(AND(D139="",E139=""),"",SUM($D$13:D139)-SUM($E$13:E139))</f>
         <v/>
       </c>
@@ -5296,7 +5293,7 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="9" t="n"/>
       <c r="E140" s="9" t="n"/>
-      <c r="F140" s="18">
+      <c r="F140" s="19">
         <f>IF(AND(D140="",E140=""),"",SUM($D$13:D140)-SUM($E$13:E140))</f>
         <v/>
       </c>
@@ -5309,7 +5306,7 @@
       <c r="C141" s="7" t="n"/>
       <c r="D141" s="9" t="n"/>
       <c r="E141" s="9" t="n"/>
-      <c r="F141" s="18">
+      <c r="F141" s="19">
         <f>IF(AND(D141="",E141=""),"",SUM($D$13:D141)-SUM($E$13:E141))</f>
         <v/>
       </c>
@@ -5322,7 +5319,7 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="9" t="n"/>
       <c r="E142" s="9" t="n"/>
-      <c r="F142" s="18">
+      <c r="F142" s="19">
         <f>IF(AND(D142="",E142=""),"",SUM($D$13:D142)-SUM($E$13:E142))</f>
         <v/>
       </c>
@@ -5335,7 +5332,7 @@
       <c r="C143" s="7" t="n"/>
       <c r="D143" s="9" t="n"/>
       <c r="E143" s="9" t="n"/>
-      <c r="F143" s="18">
+      <c r="F143" s="19">
         <f>IF(AND(D143="",E143=""),"",SUM($D$13:D143)-SUM($E$13:E143))</f>
         <v/>
       </c>
@@ -5348,7 +5345,7 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="9" t="n"/>
       <c r="E144" s="9" t="n"/>
-      <c r="F144" s="18">
+      <c r="F144" s="19">
         <f>IF(AND(D144="",E144=""),"",SUM($D$13:D144)-SUM($E$13:E144))</f>
         <v/>
       </c>
@@ -5361,7 +5358,7 @@
       <c r="C145" s="7" t="n"/>
       <c r="D145" s="9" t="n"/>
       <c r="E145" s="9" t="n"/>
-      <c r="F145" s="18">
+      <c r="F145" s="19">
         <f>IF(AND(D145="",E145=""),"",SUM($D$13:D145)-SUM($E$13:E145))</f>
         <v/>
       </c>
@@ -5374,7 +5371,7 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="9" t="n"/>
       <c r="E146" s="9" t="n"/>
-      <c r="F146" s="18">
+      <c r="F146" s="19">
         <f>IF(AND(D146="",E146=""),"",SUM($D$13:D146)-SUM($E$13:E146))</f>
         <v/>
       </c>
@@ -5387,7 +5384,7 @@
       <c r="C147" s="7" t="n"/>
       <c r="D147" s="9" t="n"/>
       <c r="E147" s="9" t="n"/>
-      <c r="F147" s="18">
+      <c r="F147" s="19">
         <f>IF(AND(D147="",E147=""),"",SUM($D$13:D147)-SUM($E$13:E147))</f>
         <v/>
       </c>
@@ -5400,7 +5397,7 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="9" t="n"/>
       <c r="E148" s="9" t="n"/>
-      <c r="F148" s="18">
+      <c r="F148" s="19">
         <f>IF(AND(D148="",E148=""),"",SUM($D$13:D148)-SUM($E$13:E148))</f>
         <v/>
       </c>
@@ -5413,7 +5410,7 @@
       <c r="C149" s="7" t="n"/>
       <c r="D149" s="9" t="n"/>
       <c r="E149" s="9" t="n"/>
-      <c r="F149" s="18">
+      <c r="F149" s="19">
         <f>IF(AND(D149="",E149=""),"",SUM($D$13:D149)-SUM($E$13:E149))</f>
         <v/>
       </c>
@@ -5426,7 +5423,7 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="9" t="n"/>
       <c r="E150" s="9" t="n"/>
-      <c r="F150" s="18">
+      <c r="F150" s="19">
         <f>IF(AND(D150="",E150=""),"",SUM($D$13:D150)-SUM($E$13:E150))</f>
         <v/>
       </c>
@@ -5439,7 +5436,7 @@
       <c r="C151" s="7" t="n"/>
       <c r="D151" s="9" t="n"/>
       <c r="E151" s="9" t="n"/>
-      <c r="F151" s="18">
+      <c r="F151" s="19">
         <f>IF(AND(D151="",E151=""),"",SUM($D$13:D151)-SUM($E$13:E151))</f>
         <v/>
       </c>
@@ -5452,7 +5449,7 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="9" t="n"/>
       <c r="E152" s="9" t="n"/>
-      <c r="F152" s="18">
+      <c r="F152" s="19">
         <f>IF(AND(D152="",E152=""),"",SUM($D$13:D152)-SUM($E$13:E152))</f>
         <v/>
       </c>
@@ -5465,7 +5462,7 @@
       <c r="C153" s="7" t="n"/>
       <c r="D153" s="9" t="n"/>
       <c r="E153" s="9" t="n"/>
-      <c r="F153" s="18">
+      <c r="F153" s="19">
         <f>IF(AND(D153="",E153=""),"",SUM($D$13:D153)-SUM($E$13:E153))</f>
         <v/>
       </c>
@@ -5478,7 +5475,7 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="9" t="n"/>
       <c r="E154" s="9" t="n"/>
-      <c r="F154" s="18">
+      <c r="F154" s="19">
         <f>IF(AND(D154="",E154=""),"",SUM($D$13:D154)-SUM($E$13:E154))</f>
         <v/>
       </c>
@@ -5491,7 +5488,7 @@
       <c r="C155" s="7" t="n"/>
       <c r="D155" s="9" t="n"/>
       <c r="E155" s="9" t="n"/>
-      <c r="F155" s="18">
+      <c r="F155" s="19">
         <f>IF(AND(D155="",E155=""),"",SUM($D$13:D155)-SUM($E$13:E155))</f>
         <v/>
       </c>
@@ -5504,7 +5501,7 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="9" t="n"/>
       <c r="E156" s="9" t="n"/>
-      <c r="F156" s="18">
+      <c r="F156" s="19">
         <f>IF(AND(D156="",E156=""),"",SUM($D$13:D156)-SUM($E$13:E156))</f>
         <v/>
       </c>
@@ -5517,7 +5514,7 @@
       <c r="C157" s="7" t="n"/>
       <c r="D157" s="9" t="n"/>
       <c r="E157" s="9" t="n"/>
-      <c r="F157" s="18">
+      <c r="F157" s="19">
         <f>IF(AND(D157="",E157=""),"",SUM($D$13:D157)-SUM($E$13:E157))</f>
         <v/>
       </c>
@@ -5530,7 +5527,7 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="9" t="n"/>
       <c r="E158" s="9" t="n"/>
-      <c r="F158" s="18">
+      <c r="F158" s="19">
         <f>IF(AND(D158="",E158=""),"",SUM($D$13:D158)-SUM($E$13:E158))</f>
         <v/>
       </c>
@@ -5543,7 +5540,7 @@
       <c r="C159" s="7" t="n"/>
       <c r="D159" s="9" t="n"/>
       <c r="E159" s="9" t="n"/>
-      <c r="F159" s="18">
+      <c r="F159" s="19">
         <f>IF(AND(D159="",E159=""),"",SUM($D$13:D159)-SUM($E$13:E159))</f>
         <v/>
       </c>
@@ -5556,7 +5553,7 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="9" t="n"/>
       <c r="E160" s="9" t="n"/>
-      <c r="F160" s="18">
+      <c r="F160" s="19">
         <f>IF(AND(D160="",E160=""),"",SUM($D$13:D160)-SUM($E$13:E160))</f>
         <v/>
       </c>
@@ -5569,7 +5566,7 @@
       <c r="C161" s="7" t="n"/>
       <c r="D161" s="9" t="n"/>
       <c r="E161" s="9" t="n"/>
-      <c r="F161" s="18">
+      <c r="F161" s="19">
         <f>IF(AND(D161="",E161=""),"",SUM($D$13:D161)-SUM($E$13:E161))</f>
         <v/>
       </c>
@@ -5582,7 +5579,7 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="9" t="n"/>
       <c r="E162" s="9" t="n"/>
-      <c r="F162" s="18">
+      <c r="F162" s="19">
         <f>IF(AND(D162="",E162=""),"",SUM($D$13:D162)-SUM($E$13:E162))</f>
         <v/>
       </c>
@@ -5595,7 +5592,7 @@
       <c r="C163" s="7" t="n"/>
       <c r="D163" s="9" t="n"/>
       <c r="E163" s="9" t="n"/>
-      <c r="F163" s="18">
+      <c r="F163" s="19">
         <f>IF(AND(D163="",E163=""),"",SUM($D$13:D163)-SUM($E$13:E163))</f>
         <v/>
       </c>
@@ -5608,7 +5605,7 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="9" t="n"/>
       <c r="E164" s="9" t="n"/>
-      <c r="F164" s="18">
+      <c r="F164" s="19">
         <f>IF(AND(D164="",E164=""),"",SUM($D$13:D164)-SUM($E$13:E164))</f>
         <v/>
       </c>
@@ -5621,7 +5618,7 @@
       <c r="C165" s="7" t="n"/>
       <c r="D165" s="9" t="n"/>
       <c r="E165" s="9" t="n"/>
-      <c r="F165" s="18">
+      <c r="F165" s="19">
         <f>IF(AND(D165="",E165=""),"",SUM($D$13:D165)-SUM($E$13:E165))</f>
         <v/>
       </c>
@@ -5634,7 +5631,7 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="9" t="n"/>
       <c r="E166" s="9" t="n"/>
-      <c r="F166" s="18">
+      <c r="F166" s="19">
         <f>IF(AND(D166="",E166=""),"",SUM($D$13:D166)-SUM($E$13:E166))</f>
         <v/>
       </c>
@@ -5647,7 +5644,7 @@
       <c r="C167" s="7" t="n"/>
       <c r="D167" s="9" t="n"/>
       <c r="E167" s="9" t="n"/>
-      <c r="F167" s="18">
+      <c r="F167" s="19">
         <f>IF(AND(D167="",E167=""),"",SUM($D$13:D167)-SUM($E$13:E167))</f>
         <v/>
       </c>
@@ -5660,7 +5657,7 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="9" t="n"/>
       <c r="E168" s="9" t="n"/>
-      <c r="F168" s="18">
+      <c r="F168" s="19">
         <f>IF(AND(D168="",E168=""),"",SUM($D$13:D168)-SUM($E$13:E168))</f>
         <v/>
       </c>
@@ -5673,7 +5670,7 @@
       <c r="C169" s="7" t="n"/>
       <c r="D169" s="9" t="n"/>
       <c r="E169" s="9" t="n"/>
-      <c r="F169" s="18">
+      <c r="F169" s="19">
         <f>IF(AND(D169="",E169=""),"",SUM($D$13:D169)-SUM($E$13:E169))</f>
         <v/>
       </c>
@@ -5686,7 +5683,7 @@
       <c r="C170" s="7" t="n"/>
       <c r="D170" s="9" t="n"/>
       <c r="E170" s="9" t="n"/>
-      <c r="F170" s="18">
+      <c r="F170" s="19">
         <f>IF(AND(D170="",E170=""),"",SUM($D$13:D170)-SUM($E$13:E170))</f>
         <v/>
       </c>
@@ -5699,7 +5696,7 @@
       <c r="C171" s="7" t="n"/>
       <c r="D171" s="9" t="n"/>
       <c r="E171" s="9" t="n"/>
-      <c r="F171" s="18">
+      <c r="F171" s="19">
         <f>IF(AND(D171="",E171=""),"",SUM($D$13:D171)-SUM($E$13:E171))</f>
         <v/>
       </c>
@@ -5712,7 +5709,7 @@
       <c r="C172" s="7" t="n"/>
       <c r="D172" s="9" t="n"/>
       <c r="E172" s="9" t="n"/>
-      <c r="F172" s="18">
+      <c r="F172" s="19">
         <f>IF(AND(D172="",E172=""),"",SUM($D$13:D172)-SUM($E$13:E172))</f>
         <v/>
       </c>
@@ -5725,7 +5722,7 @@
       <c r="C173" s="7" t="n"/>
       <c r="D173" s="9" t="n"/>
       <c r="E173" s="9" t="n"/>
-      <c r="F173" s="18">
+      <c r="F173" s="19">
         <f>IF(AND(D173="",E173=""),"",SUM($D$13:D173)-SUM($E$13:E173))</f>
         <v/>
       </c>
@@ -5738,7 +5735,7 @@
       <c r="C174" s="7" t="n"/>
       <c r="D174" s="9" t="n"/>
       <c r="E174" s="9" t="n"/>
-      <c r="F174" s="18">
+      <c r="F174" s="19">
         <f>IF(AND(D174="",E174=""),"",SUM($D$13:D174)-SUM($E$13:E174))</f>
         <v/>
       </c>
@@ -5751,7 +5748,7 @@
       <c r="C175" s="7" t="n"/>
       <c r="D175" s="9" t="n"/>
       <c r="E175" s="9" t="n"/>
-      <c r="F175" s="18">
+      <c r="F175" s="19">
         <f>IF(AND(D175="",E175=""),"",SUM($D$13:D175)-SUM($E$13:E175))</f>
         <v/>
       </c>
@@ -5764,7 +5761,7 @@
       <c r="C176" s="7" t="n"/>
       <c r="D176" s="9" t="n"/>
       <c r="E176" s="9" t="n"/>
-      <c r="F176" s="18">
+      <c r="F176" s="19">
         <f>IF(AND(D176="",E176=""),"",SUM($D$13:D176)-SUM($E$13:E176))</f>
         <v/>
       </c>
@@ -5777,7 +5774,7 @@
       <c r="C177" s="7" t="n"/>
       <c r="D177" s="9" t="n"/>
       <c r="E177" s="9" t="n"/>
-      <c r="F177" s="18">
+      <c r="F177" s="19">
         <f>IF(AND(D177="",E177=""),"",SUM($D$13:D177)-SUM($E$13:E177))</f>
         <v/>
       </c>
@@ -5790,7 +5787,7 @@
       <c r="C178" s="7" t="n"/>
       <c r="D178" s="9" t="n"/>
       <c r="E178" s="9" t="n"/>
-      <c r="F178" s="18">
+      <c r="F178" s="19">
         <f>IF(AND(D178="",E178=""),"",SUM($D$13:D178)-SUM($E$13:E178))</f>
         <v/>
       </c>
@@ -5803,7 +5800,7 @@
       <c r="C179" s="7" t="n"/>
       <c r="D179" s="9" t="n"/>
       <c r="E179" s="9" t="n"/>
-      <c r="F179" s="18">
+      <c r="F179" s="19">
         <f>IF(AND(D179="",E179=""),"",SUM($D$13:D179)-SUM($E$13:E179))</f>
         <v/>
       </c>
@@ -5816,7 +5813,7 @@
       <c r="C180" s="7" t="n"/>
       <c r="D180" s="9" t="n"/>
       <c r="E180" s="9" t="n"/>
-      <c r="F180" s="18">
+      <c r="F180" s="19">
         <f>IF(AND(D180="",E180=""),"",SUM($D$13:D180)-SUM($E$13:E180))</f>
         <v/>
       </c>
@@ -5829,7 +5826,7 @@
       <c r="C181" s="7" t="n"/>
       <c r="D181" s="9" t="n"/>
       <c r="E181" s="9" t="n"/>
-      <c r="F181" s="18">
+      <c r="F181" s="19">
         <f>IF(AND(D181="",E181=""),"",SUM($D$13:D181)-SUM($E$13:E181))</f>
         <v/>
       </c>
@@ -5842,7 +5839,7 @@
       <c r="C182" s="7" t="n"/>
       <c r="D182" s="9" t="n"/>
       <c r="E182" s="9" t="n"/>
-      <c r="F182" s="18">
+      <c r="F182" s="19">
         <f>IF(AND(D182="",E182=""),"",SUM($D$13:D182)-SUM($E$13:E182))</f>
         <v/>
       </c>
@@ -5855,7 +5852,7 @@
       <c r="C183" s="7" t="n"/>
       <c r="D183" s="9" t="n"/>
       <c r="E183" s="9" t="n"/>
-      <c r="F183" s="18">
+      <c r="F183" s="19">
         <f>IF(AND(D183="",E183=""),"",SUM($D$13:D183)-SUM($E$13:E183))</f>
         <v/>
       </c>
@@ -5868,7 +5865,7 @@
       <c r="C184" s="7" t="n"/>
       <c r="D184" s="9" t="n"/>
       <c r="E184" s="9" t="n"/>
-      <c r="F184" s="18">
+      <c r="F184" s="19">
         <f>IF(AND(D184="",E184=""),"",SUM($D$13:D184)-SUM($E$13:E184))</f>
         <v/>
       </c>
@@ -5881,7 +5878,7 @@
       <c r="C185" s="7" t="n"/>
       <c r="D185" s="9" t="n"/>
       <c r="E185" s="9" t="n"/>
-      <c r="F185" s="18">
+      <c r="F185" s="19">
         <f>IF(AND(D185="",E185=""),"",SUM($D$13:D185)-SUM($E$13:E185))</f>
         <v/>
       </c>
@@ -5894,7 +5891,7 @@
       <c r="C186" s="7" t="n"/>
       <c r="D186" s="9" t="n"/>
       <c r="E186" s="9" t="n"/>
-      <c r="F186" s="18">
+      <c r="F186" s="19">
         <f>IF(AND(D186="",E186=""),"",SUM($D$13:D186)-SUM($E$13:E186))</f>
         <v/>
       </c>
@@ -5907,7 +5904,7 @@
       <c r="C187" s="7" t="n"/>
       <c r="D187" s="9" t="n"/>
       <c r="E187" s="9" t="n"/>
-      <c r="F187" s="18">
+      <c r="F187" s="19">
         <f>IF(AND(D187="",E187=""),"",SUM($D$13:D187)-SUM($E$13:E187))</f>
         <v/>
       </c>
@@ -5920,7 +5917,7 @@
       <c r="C188" s="7" t="n"/>
       <c r="D188" s="9" t="n"/>
       <c r="E188" s="9" t="n"/>
-      <c r="F188" s="18">
+      <c r="F188" s="19">
         <f>IF(AND(D188="",E188=""),"",SUM($D$13:D188)-SUM($E$13:E188))</f>
         <v/>
       </c>
@@ -5933,7 +5930,7 @@
       <c r="C189" s="7" t="n"/>
       <c r="D189" s="9" t="n"/>
       <c r="E189" s="9" t="n"/>
-      <c r="F189" s="18">
+      <c r="F189" s="19">
         <f>IF(AND(D189="",E189=""),"",SUM($D$13:D189)-SUM($E$13:E189))</f>
         <v/>
       </c>
@@ -5946,7 +5943,7 @@
       <c r="C190" s="7" t="n"/>
       <c r="D190" s="9" t="n"/>
       <c r="E190" s="9" t="n"/>
-      <c r="F190" s="18">
+      <c r="F190" s="19">
         <f>IF(AND(D190="",E190=""),"",SUM($D$13:D190)-SUM($E$13:E190))</f>
         <v/>
       </c>
@@ -5959,7 +5956,7 @@
       <c r="C191" s="7" t="n"/>
       <c r="D191" s="9" t="n"/>
       <c r="E191" s="9" t="n"/>
-      <c r="F191" s="18">
+      <c r="F191" s="19">
         <f>IF(AND(D191="",E191=""),"",SUM($D$13:D191)-SUM($E$13:E191))</f>
         <v/>
       </c>
@@ -5972,7 +5969,7 @@
       <c r="C192" s="7" t="n"/>
       <c r="D192" s="9" t="n"/>
       <c r="E192" s="9" t="n"/>
-      <c r="F192" s="18">
+      <c r="F192" s="19">
         <f>IF(AND(D192="",E192=""),"",SUM($D$13:D192)-SUM($E$13:E192))</f>
         <v/>
       </c>
@@ -5985,7 +5982,7 @@
       <c r="C193" s="7" t="n"/>
       <c r="D193" s="9" t="n"/>
       <c r="E193" s="9" t="n"/>
-      <c r="F193" s="18">
+      <c r="F193" s="19">
         <f>IF(AND(D193="",E193=""),"",SUM($D$13:D193)-SUM($E$13:E193))</f>
         <v/>
       </c>
@@ -5998,7 +5995,7 @@
       <c r="C194" s="7" t="n"/>
       <c r="D194" s="9" t="n"/>
       <c r="E194" s="9" t="n"/>
-      <c r="F194" s="18">
+      <c r="F194" s="19">
         <f>IF(AND(D194="",E194=""),"",SUM($D$13:D194)-SUM($E$13:E194))</f>
         <v/>
       </c>
@@ -6011,7 +6008,7 @@
       <c r="C195" s="7" t="n"/>
       <c r="D195" s="9" t="n"/>
       <c r="E195" s="9" t="n"/>
-      <c r="F195" s="18">
+      <c r="F195" s="19">
         <f>IF(AND(D195="",E195=""),"",SUM($D$13:D195)-SUM($E$13:E195))</f>
         <v/>
       </c>
@@ -6024,7 +6021,7 @@
       <c r="C196" s="7" t="n"/>
       <c r="D196" s="9" t="n"/>
       <c r="E196" s="9" t="n"/>
-      <c r="F196" s="18">
+      <c r="F196" s="19">
         <f>IF(AND(D196="",E196=""),"",SUM($D$13:D196)-SUM($E$13:E196))</f>
         <v/>
       </c>
@@ -6037,7 +6034,7 @@
       <c r="C197" s="7" t="n"/>
       <c r="D197" s="9" t="n"/>
       <c r="E197" s="9" t="n"/>
-      <c r="F197" s="18">
+      <c r="F197" s="19">
         <f>IF(AND(D197="",E197=""),"",SUM($D$13:D197)-SUM($E$13:E197))</f>
         <v/>
       </c>
@@ -6050,7 +6047,7 @@
       <c r="C198" s="7" t="n"/>
       <c r="D198" s="9" t="n"/>
       <c r="E198" s="9" t="n"/>
-      <c r="F198" s="18">
+      <c r="F198" s="19">
         <f>IF(AND(D198="",E198=""),"",SUM($D$13:D198)-SUM($E$13:E198))</f>
         <v/>
       </c>
@@ -6063,7 +6060,7 @@
       <c r="C199" s="7" t="n"/>
       <c r="D199" s="9" t="n"/>
       <c r="E199" s="9" t="n"/>
-      <c r="F199" s="18">
+      <c r="F199" s="19">
         <f>IF(AND(D199="",E199=""),"",SUM($D$13:D199)-SUM($E$13:E199))</f>
         <v/>
       </c>
@@ -6076,7 +6073,7 @@
       <c r="C200" s="7" t="n"/>
       <c r="D200" s="9" t="n"/>
       <c r="E200" s="9" t="n"/>
-      <c r="F200" s="18">
+      <c r="F200" s="19">
         <f>IF(AND(D200="",E200=""),"",SUM($D$13:D200)-SUM($E$13:E200))</f>
         <v/>
       </c>
@@ -6089,7 +6086,7 @@
       <c r="C201" s="7" t="n"/>
       <c r="D201" s="9" t="n"/>
       <c r="E201" s="9" t="n"/>
-      <c r="F201" s="18">
+      <c r="F201" s="19">
         <f>IF(AND(D201="",E201=""),"",SUM($D$13:D201)-SUM($E$13:E201))</f>
         <v/>
       </c>
@@ -6102,7 +6099,7 @@
       <c r="C202" s="7" t="n"/>
       <c r="D202" s="9" t="n"/>
       <c r="E202" s="9" t="n"/>
-      <c r="F202" s="18">
+      <c r="F202" s="19">
         <f>IF(AND(D202="",E202=""),"",SUM($D$13:D202)-SUM($E$13:E202))</f>
         <v/>
       </c>
@@ -6115,7 +6112,7 @@
       <c r="C203" s="7" t="n"/>
       <c r="D203" s="9" t="n"/>
       <c r="E203" s="9" t="n"/>
-      <c r="F203" s="18">
+      <c r="F203" s="19">
         <f>IF(AND(D203="",E203=""),"",SUM($D$13:D203)-SUM($E$13:E203))</f>
         <v/>
       </c>
@@ -6128,7 +6125,7 @@
       <c r="C204" s="7" t="n"/>
       <c r="D204" s="9" t="n"/>
       <c r="E204" s="9" t="n"/>
-      <c r="F204" s="18">
+      <c r="F204" s="19">
         <f>IF(AND(D204="",E204=""),"",SUM($D$13:D204)-SUM($E$13:E204))</f>
         <v/>
       </c>
@@ -6141,7 +6138,7 @@
       <c r="C205" s="7" t="n"/>
       <c r="D205" s="9" t="n"/>
       <c r="E205" s="9" t="n"/>
-      <c r="F205" s="18">
+      <c r="F205" s="19">
         <f>IF(AND(D205="",E205=""),"",SUM($D$13:D205)-SUM($E$13:E205))</f>
         <v/>
       </c>
@@ -6154,7 +6151,7 @@
       <c r="C206" s="7" t="n"/>
       <c r="D206" s="9" t="n"/>
       <c r="E206" s="9" t="n"/>
-      <c r="F206" s="18">
+      <c r="F206" s="19">
         <f>IF(AND(D206="",E206=""),"",SUM($D$13:D206)-SUM($E$13:E206))</f>
         <v/>
       </c>
@@ -6167,7 +6164,7 @@
       <c r="C207" s="7" t="n"/>
       <c r="D207" s="9" t="n"/>
       <c r="E207" s="9" t="n"/>
-      <c r="F207" s="18">
+      <c r="F207" s="19">
         <f>IF(AND(D207="",E207=""),"",SUM($D$13:D207)-SUM($E$13:E207))</f>
         <v/>
       </c>
@@ -6180,7 +6177,7 @@
       <c r="C208" s="7" t="n"/>
       <c r="D208" s="9" t="n"/>
       <c r="E208" s="9" t="n"/>
-      <c r="F208" s="18">
+      <c r="F208" s="19">
         <f>IF(AND(D208="",E208=""),"",SUM($D$13:D208)-SUM($E$13:E208))</f>
         <v/>
       </c>
@@ -6193,7 +6190,7 @@
       <c r="C209" s="7" t="n"/>
       <c r="D209" s="9" t="n"/>
       <c r="E209" s="9" t="n"/>
-      <c r="F209" s="18">
+      <c r="F209" s="19">
         <f>IF(AND(D209="",E209=""),"",SUM($D$13:D209)-SUM($E$13:E209))</f>
         <v/>
       </c>
@@ -6206,7 +6203,7 @@
       <c r="C210" s="7" t="n"/>
       <c r="D210" s="9" t="n"/>
       <c r="E210" s="9" t="n"/>
-      <c r="F210" s="18">
+      <c r="F210" s="19">
         <f>IF(AND(D210="",E210=""),"",SUM($D$13:D210)-SUM($E$13:E210))</f>
         <v/>
       </c>
@@ -6219,7 +6216,7 @@
       <c r="C211" s="7" t="n"/>
       <c r="D211" s="9" t="n"/>
       <c r="E211" s="9" t="n"/>
-      <c r="F211" s="18">
+      <c r="F211" s="19">
         <f>IF(AND(D211="",E211=""),"",SUM($D$13:D211)-SUM($E$13:E211))</f>
         <v/>
       </c>
@@ -6232,7 +6229,7 @@
       <c r="C212" s="7" t="n"/>
       <c r="D212" s="9" t="n"/>
       <c r="E212" s="9" t="n"/>
-      <c r="F212" s="18">
+      <c r="F212" s="19">
         <f>IF(AND(D212="",E212=""),"",SUM($D$13:D212)-SUM($E$13:E212))</f>
         <v/>
       </c>
@@ -6340,8 +6337,8 @@
           <t>Creditor window closes on</t>
         </is>
       </c>
-      <c r="B5" s="19">
-        <f>'Start here'!B25</f>
+      <c r="B5" s="20">
+        <f>IF('Start here'!B25="","",'Start here'!B25)</f>
         <v/>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6357,12 +6354,12 @@
       <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Total claimed</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <f>SUM($C$12:$C$211)</f>
         <v/>
       </c>
@@ -6375,12 +6372,12 @@
       <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Total allowed</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <f>SUM($G$12:$G$211)</f>
         <v/>
       </c>
@@ -6393,12 +6390,12 @@
       <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Total paid (from Ledger, category 'debt paid')</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"debt paid",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
@@ -6411,12 +6408,12 @@
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Claims still pending (count)</t>
         </is>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="11">
         <f>COUNTIF($F$12:$F$211,"pending")</f>
         <v/>
       </c>
@@ -6440,164 +6437,158 @@
       <c r="I10" s="2" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Creditor</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Date received</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Amount claimed</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Secured?</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Documentation received?</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Amount allowed</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>Date paid</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Capital One (card ending 2210)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="18" t="n">
+        <v>46132</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>3412.77</v>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>allowed</t>
         </is>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>3412.77</v>
       </c>
       <c r="H12" s="8" t="n"/>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>Statement matches date-of-death balance</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Miami Valley Hospital</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="18" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C13" s="17" t="n">
         <v>8900</v>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>disputed</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="8" t="n"/>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>Itemized bill requested 2026-05-03; Medicare not yet billed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Late claim: Acme Collections</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="18" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C14" s="17" t="n">
         <v>640</v>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>rejected</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="8" t="n"/>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>Received after window; rejection letter sent</t>
         </is>
@@ -8864,12 +8855,12 @@
       <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Balance in estate account</t>
         </is>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <f>Ledger!B7</f>
         <v/>
       </c>
@@ -8881,12 +8872,12 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Less: reserve for taxes and final costs</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <f>'Start here'!B26</f>
         <v/>
       </c>
@@ -8898,12 +8889,12 @@
       <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Less: specific gifts (dollar amounts below)</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <f>SUM($C$13:$C$62)</f>
         <v/>
       </c>
@@ -8920,7 +8911,7 @@
           <t>Available for percentage shares</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>B5-B6-B7</f>
         <v/>
       </c>
@@ -8932,12 +8923,12 @@
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Percentages entered (should total 100%)</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>SUM($B$13:$B$62)</f>
         <v/>
       </c>
@@ -8973,134 +8964,134 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Beneficiary</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Specific gift ($)</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Computed share</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Paid so far</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Balance owed</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Receipt &amp; release signed?</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Anna Kowalski (daughter)</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>IF(A13="","",IF(C13&lt;&gt;"",C13,$B$8*B13))</f>
         <v/>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>IF(A13="","",D13-N(E13))</f>
         <v/>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Address on file</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Mark Kowalski (son)</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="C14" s="9" t="n"/>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f>IF(A14="","",IF(C14&lt;&gt;"",C14,$B$8*B14))</f>
         <v/>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <f>IF(A14="","",D14-N(E14))</f>
         <v/>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr"/>
+      <c r="H14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>St. Luke's Parish (specific gift, will §4)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <f>IF(A15="","",IF(C15&lt;&gt;"",C15,$B$8*B15))</f>
         <v/>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <f>IF(A15="","",D15-N(E15))</f>
         <v/>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Pay after window closes</t>
         </is>
@@ -9108,14 +9099,14 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
-      <c r="B16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="18">
+      <c r="D16" s="19">
         <f>IF(A16="","",IF(C16&lt;&gt;"",C16,$B$8*B16))</f>
         <v/>
       </c>
       <c r="E16" s="9" t="n"/>
-      <c r="F16" s="18">
+      <c r="F16" s="19">
         <f>IF(A16="","",D16-N(E16))</f>
         <v/>
       </c>
@@ -9124,14 +9115,14 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
-      <c r="B17" s="22" t="n"/>
+      <c r="B17" s="23" t="n"/>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="18">
+      <c r="D17" s="19">
         <f>IF(A17="","",IF(C17&lt;&gt;"",C17,$B$8*B17))</f>
         <v/>
       </c>
       <c r="E17" s="9" t="n"/>
-      <c r="F17" s="18">
+      <c r="F17" s="19">
         <f>IF(A17="","",D17-N(E17))</f>
         <v/>
       </c>
@@ -9140,14 +9131,14 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
-      <c r="B18" s="22" t="n"/>
+      <c r="B18" s="23" t="n"/>
       <c r="C18" s="9" t="n"/>
-      <c r="D18" s="18">
+      <c r="D18" s="19">
         <f>IF(A18="","",IF(C18&lt;&gt;"",C18,$B$8*B18))</f>
         <v/>
       </c>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="18">
+      <c r="F18" s="19">
         <f>IF(A18="","",D18-N(E18))</f>
         <v/>
       </c>
@@ -9156,14 +9147,14 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
-      <c r="B19" s="22" t="n"/>
+      <c r="B19" s="23" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="18">
+      <c r="D19" s="19">
         <f>IF(A19="","",IF(C19&lt;&gt;"",C19,$B$8*B19))</f>
         <v/>
       </c>
       <c r="E19" s="9" t="n"/>
-      <c r="F19" s="18">
+      <c r="F19" s="19">
         <f>IF(A19="","",D19-N(E19))</f>
         <v/>
       </c>
@@ -9172,14 +9163,14 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="22" t="n"/>
+      <c r="B20" s="23" t="n"/>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="18">
+      <c r="D20" s="19">
         <f>IF(A20="","",IF(C20&lt;&gt;"",C20,$B$8*B20))</f>
         <v/>
       </c>
       <c r="E20" s="9" t="n"/>
-      <c r="F20" s="18">
+      <c r="F20" s="19">
         <f>IF(A20="","",D20-N(E20))</f>
         <v/>
       </c>
@@ -9188,14 +9179,14 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
-      <c r="B21" s="22" t="n"/>
+      <c r="B21" s="23" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="18">
+      <c r="D21" s="19">
         <f>IF(A21="","",IF(C21&lt;&gt;"",C21,$B$8*B21))</f>
         <v/>
       </c>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <f>IF(A21="","",D21-N(E21))</f>
         <v/>
       </c>
@@ -9204,14 +9195,14 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
-      <c r="B22" s="22" t="n"/>
+      <c r="B22" s="23" t="n"/>
       <c r="C22" s="9" t="n"/>
-      <c r="D22" s="18">
+      <c r="D22" s="19">
         <f>IF(A22="","",IF(C22&lt;&gt;"",C22,$B$8*B22))</f>
         <v/>
       </c>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <f>IF(A22="","",D22-N(E22))</f>
         <v/>
       </c>
@@ -9220,14 +9211,14 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
-      <c r="B23" s="22" t="n"/>
+      <c r="B23" s="23" t="n"/>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="18">
+      <c r="D23" s="19">
         <f>IF(A23="","",IF(C23&lt;&gt;"",C23,$B$8*B23))</f>
         <v/>
       </c>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <f>IF(A23="","",D23-N(E23))</f>
         <v/>
       </c>
@@ -9236,14 +9227,14 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="22" t="n"/>
+      <c r="B24" s="23" t="n"/>
       <c r="C24" s="9" t="n"/>
-      <c r="D24" s="18">
+      <c r="D24" s="19">
         <f>IF(A24="","",IF(C24&lt;&gt;"",C24,$B$8*B24))</f>
         <v/>
       </c>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <f>IF(A24="","",D24-N(E24))</f>
         <v/>
       </c>
@@ -9252,14 +9243,14 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
-      <c r="B25" s="22" t="n"/>
+      <c r="B25" s="23" t="n"/>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="18">
+      <c r="D25" s="19">
         <f>IF(A25="","",IF(C25&lt;&gt;"",C25,$B$8*B25))</f>
         <v/>
       </c>
       <c r="E25" s="9" t="n"/>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <f>IF(A25="","",D25-N(E25))</f>
         <v/>
       </c>
@@ -9268,14 +9259,14 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
-      <c r="B26" s="22" t="n"/>
+      <c r="B26" s="23" t="n"/>
       <c r="C26" s="9" t="n"/>
-      <c r="D26" s="18">
+      <c r="D26" s="19">
         <f>IF(A26="","",IF(C26&lt;&gt;"",C26,$B$8*B26))</f>
         <v/>
       </c>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="18">
+      <c r="F26" s="19">
         <f>IF(A26="","",D26-N(E26))</f>
         <v/>
       </c>
@@ -9284,14 +9275,14 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
-      <c r="B27" s="22" t="n"/>
+      <c r="B27" s="23" t="n"/>
       <c r="C27" s="9" t="n"/>
-      <c r="D27" s="18">
+      <c r="D27" s="19">
         <f>IF(A27="","",IF(C27&lt;&gt;"",C27,$B$8*B27))</f>
         <v/>
       </c>
       <c r="E27" s="9" t="n"/>
-      <c r="F27" s="18">
+      <c r="F27" s="19">
         <f>IF(A27="","",D27-N(E27))</f>
         <v/>
       </c>
@@ -9300,14 +9291,14 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
-      <c r="B28" s="22" t="n"/>
+      <c r="B28" s="23" t="n"/>
       <c r="C28" s="9" t="n"/>
-      <c r="D28" s="18">
+      <c r="D28" s="19">
         <f>IF(A28="","",IF(C28&lt;&gt;"",C28,$B$8*B28))</f>
         <v/>
       </c>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="18">
+      <c r="F28" s="19">
         <f>IF(A28="","",D28-N(E28))</f>
         <v/>
       </c>
@@ -9316,14 +9307,14 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
-      <c r="B29" s="22" t="n"/>
+      <c r="B29" s="23" t="n"/>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="18">
+      <c r="D29" s="19">
         <f>IF(A29="","",IF(C29&lt;&gt;"",C29,$B$8*B29))</f>
         <v/>
       </c>
       <c r="E29" s="9" t="n"/>
-      <c r="F29" s="18">
+      <c r="F29" s="19">
         <f>IF(A29="","",D29-N(E29))</f>
         <v/>
       </c>
@@ -9332,14 +9323,14 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
-      <c r="B30" s="22" t="n"/>
+      <c r="B30" s="23" t="n"/>
       <c r="C30" s="9" t="n"/>
-      <c r="D30" s="18">
+      <c r="D30" s="19">
         <f>IF(A30="","",IF(C30&lt;&gt;"",C30,$B$8*B30))</f>
         <v/>
       </c>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="18">
+      <c r="F30" s="19">
         <f>IF(A30="","",D30-N(E30))</f>
         <v/>
       </c>
@@ -9348,14 +9339,14 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
-      <c r="B31" s="22" t="n"/>
+      <c r="B31" s="23" t="n"/>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="18">
+      <c r="D31" s="19">
         <f>IF(A31="","",IF(C31&lt;&gt;"",C31,$B$8*B31))</f>
         <v/>
       </c>
       <c r="E31" s="9" t="n"/>
-      <c r="F31" s="18">
+      <c r="F31" s="19">
         <f>IF(A31="","",D31-N(E31))</f>
         <v/>
       </c>
@@ -9364,14 +9355,14 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
-      <c r="B32" s="22" t="n"/>
+      <c r="B32" s="23" t="n"/>
       <c r="C32" s="9" t="n"/>
-      <c r="D32" s="18">
+      <c r="D32" s="19">
         <f>IF(A32="","",IF(C32&lt;&gt;"",C32,$B$8*B32))</f>
         <v/>
       </c>
       <c r="E32" s="9" t="n"/>
-      <c r="F32" s="18">
+      <c r="F32" s="19">
         <f>IF(A32="","",D32-N(E32))</f>
         <v/>
       </c>
@@ -9380,14 +9371,14 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
-      <c r="B33" s="22" t="n"/>
+      <c r="B33" s="23" t="n"/>
       <c r="C33" s="9" t="n"/>
-      <c r="D33" s="18">
+      <c r="D33" s="19">
         <f>IF(A33="","",IF(C33&lt;&gt;"",C33,$B$8*B33))</f>
         <v/>
       </c>
       <c r="E33" s="9" t="n"/>
-      <c r="F33" s="18">
+      <c r="F33" s="19">
         <f>IF(A33="","",D33-N(E33))</f>
         <v/>
       </c>
@@ -9396,14 +9387,14 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="22" t="n"/>
+      <c r="B34" s="23" t="n"/>
       <c r="C34" s="9" t="n"/>
-      <c r="D34" s="18">
+      <c r="D34" s="19">
         <f>IF(A34="","",IF(C34&lt;&gt;"",C34,$B$8*B34))</f>
         <v/>
       </c>
       <c r="E34" s="9" t="n"/>
-      <c r="F34" s="18">
+      <c r="F34" s="19">
         <f>IF(A34="","",D34-N(E34))</f>
         <v/>
       </c>
@@ -9412,14 +9403,14 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
-      <c r="B35" s="22" t="n"/>
+      <c r="B35" s="23" t="n"/>
       <c r="C35" s="9" t="n"/>
-      <c r="D35" s="18">
+      <c r="D35" s="19">
         <f>IF(A35="","",IF(C35&lt;&gt;"",C35,$B$8*B35))</f>
         <v/>
       </c>
       <c r="E35" s="9" t="n"/>
-      <c r="F35" s="18">
+      <c r="F35" s="19">
         <f>IF(A35="","",D35-N(E35))</f>
         <v/>
       </c>
@@ -9428,14 +9419,14 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
-      <c r="B36" s="22" t="n"/>
+      <c r="B36" s="23" t="n"/>
       <c r="C36" s="9" t="n"/>
-      <c r="D36" s="18">
+      <c r="D36" s="19">
         <f>IF(A36="","",IF(C36&lt;&gt;"",C36,$B$8*B36))</f>
         <v/>
       </c>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="18">
+      <c r="F36" s="19">
         <f>IF(A36="","",D36-N(E36))</f>
         <v/>
       </c>
@@ -9444,14 +9435,14 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
-      <c r="B37" s="22" t="n"/>
+      <c r="B37" s="23" t="n"/>
       <c r="C37" s="9" t="n"/>
-      <c r="D37" s="18">
+      <c r="D37" s="19">
         <f>IF(A37="","",IF(C37&lt;&gt;"",C37,$B$8*B37))</f>
         <v/>
       </c>
       <c r="E37" s="9" t="n"/>
-      <c r="F37" s="18">
+      <c r="F37" s="19">
         <f>IF(A37="","",D37-N(E37))</f>
         <v/>
       </c>
@@ -9460,14 +9451,14 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
-      <c r="B38" s="22" t="n"/>
+      <c r="B38" s="23" t="n"/>
       <c r="C38" s="9" t="n"/>
-      <c r="D38" s="18">
+      <c r="D38" s="19">
         <f>IF(A38="","",IF(C38&lt;&gt;"",C38,$B$8*B38))</f>
         <v/>
       </c>
       <c r="E38" s="9" t="n"/>
-      <c r="F38" s="18">
+      <c r="F38" s="19">
         <f>IF(A38="","",D38-N(E38))</f>
         <v/>
       </c>
@@ -9476,14 +9467,14 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
-      <c r="B39" s="22" t="n"/>
+      <c r="B39" s="23" t="n"/>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="18">
+      <c r="D39" s="19">
         <f>IF(A39="","",IF(C39&lt;&gt;"",C39,$B$8*B39))</f>
         <v/>
       </c>
       <c r="E39" s="9" t="n"/>
-      <c r="F39" s="18">
+      <c r="F39" s="19">
         <f>IF(A39="","",D39-N(E39))</f>
         <v/>
       </c>
@@ -9492,14 +9483,14 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
-      <c r="B40" s="22" t="n"/>
+      <c r="B40" s="23" t="n"/>
       <c r="C40" s="9" t="n"/>
-      <c r="D40" s="18">
+      <c r="D40" s="19">
         <f>IF(A40="","",IF(C40&lt;&gt;"",C40,$B$8*B40))</f>
         <v/>
       </c>
       <c r="E40" s="9" t="n"/>
-      <c r="F40" s="18">
+      <c r="F40" s="19">
         <f>IF(A40="","",D40-N(E40))</f>
         <v/>
       </c>
@@ -9508,14 +9499,14 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
-      <c r="B41" s="22" t="n"/>
+      <c r="B41" s="23" t="n"/>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="18">
+      <c r="D41" s="19">
         <f>IF(A41="","",IF(C41&lt;&gt;"",C41,$B$8*B41))</f>
         <v/>
       </c>
       <c r="E41" s="9" t="n"/>
-      <c r="F41" s="18">
+      <c r="F41" s="19">
         <f>IF(A41="","",D41-N(E41))</f>
         <v/>
       </c>
@@ -9524,14 +9515,14 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
-      <c r="B42" s="22" t="n"/>
+      <c r="B42" s="23" t="n"/>
       <c r="C42" s="9" t="n"/>
-      <c r="D42" s="18">
+      <c r="D42" s="19">
         <f>IF(A42="","",IF(C42&lt;&gt;"",C42,$B$8*B42))</f>
         <v/>
       </c>
       <c r="E42" s="9" t="n"/>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <f>IF(A42="","",D42-N(E42))</f>
         <v/>
       </c>
@@ -9540,14 +9531,14 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
-      <c r="B43" s="22" t="n"/>
+      <c r="B43" s="23" t="n"/>
       <c r="C43" s="9" t="n"/>
-      <c r="D43" s="18">
+      <c r="D43" s="19">
         <f>IF(A43="","",IF(C43&lt;&gt;"",C43,$B$8*B43))</f>
         <v/>
       </c>
       <c r="E43" s="9" t="n"/>
-      <c r="F43" s="18">
+      <c r="F43" s="19">
         <f>IF(A43="","",D43-N(E43))</f>
         <v/>
       </c>
@@ -9556,14 +9547,14 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="22" t="n"/>
+      <c r="B44" s="23" t="n"/>
       <c r="C44" s="9" t="n"/>
-      <c r="D44" s="18">
+      <c r="D44" s="19">
         <f>IF(A44="","",IF(C44&lt;&gt;"",C44,$B$8*B44))</f>
         <v/>
       </c>
       <c r="E44" s="9" t="n"/>
-      <c r="F44" s="18">
+      <c r="F44" s="19">
         <f>IF(A44="","",D44-N(E44))</f>
         <v/>
       </c>
@@ -9572,14 +9563,14 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
-      <c r="B45" s="22" t="n"/>
+      <c r="B45" s="23" t="n"/>
       <c r="C45" s="9" t="n"/>
-      <c r="D45" s="18">
+      <c r="D45" s="19">
         <f>IF(A45="","",IF(C45&lt;&gt;"",C45,$B$8*B45))</f>
         <v/>
       </c>
       <c r="E45" s="9" t="n"/>
-      <c r="F45" s="18">
+      <c r="F45" s="19">
         <f>IF(A45="","",D45-N(E45))</f>
         <v/>
       </c>
@@ -9588,14 +9579,14 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
-      <c r="B46" s="22" t="n"/>
+      <c r="B46" s="23" t="n"/>
       <c r="C46" s="9" t="n"/>
-      <c r="D46" s="18">
+      <c r="D46" s="19">
         <f>IF(A46="","",IF(C46&lt;&gt;"",C46,$B$8*B46))</f>
         <v/>
       </c>
       <c r="E46" s="9" t="n"/>
-      <c r="F46" s="18">
+      <c r="F46" s="19">
         <f>IF(A46="","",D46-N(E46))</f>
         <v/>
       </c>
@@ -9604,14 +9595,14 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
-      <c r="B47" s="22" t="n"/>
+      <c r="B47" s="23" t="n"/>
       <c r="C47" s="9" t="n"/>
-      <c r="D47" s="18">
+      <c r="D47" s="19">
         <f>IF(A47="","",IF(C47&lt;&gt;"",C47,$B$8*B47))</f>
         <v/>
       </c>
       <c r="E47" s="9" t="n"/>
-      <c r="F47" s="18">
+      <c r="F47" s="19">
         <f>IF(A47="","",D47-N(E47))</f>
         <v/>
       </c>
@@ -9620,14 +9611,14 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="22" t="n"/>
+      <c r="B48" s="23" t="n"/>
       <c r="C48" s="9" t="n"/>
-      <c r="D48" s="18">
+      <c r="D48" s="19">
         <f>IF(A48="","",IF(C48&lt;&gt;"",C48,$B$8*B48))</f>
         <v/>
       </c>
       <c r="E48" s="9" t="n"/>
-      <c r="F48" s="18">
+      <c r="F48" s="19">
         <f>IF(A48="","",D48-N(E48))</f>
         <v/>
       </c>
@@ -9636,14 +9627,14 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
-      <c r="B49" s="22" t="n"/>
+      <c r="B49" s="23" t="n"/>
       <c r="C49" s="9" t="n"/>
-      <c r="D49" s="18">
+      <c r="D49" s="19">
         <f>IF(A49="","",IF(C49&lt;&gt;"",C49,$B$8*B49))</f>
         <v/>
       </c>
       <c r="E49" s="9" t="n"/>
-      <c r="F49" s="18">
+      <c r="F49" s="19">
         <f>IF(A49="","",D49-N(E49))</f>
         <v/>
       </c>
@@ -9652,14 +9643,14 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
-      <c r="B50" s="22" t="n"/>
+      <c r="B50" s="23" t="n"/>
       <c r="C50" s="9" t="n"/>
-      <c r="D50" s="18">
+      <c r="D50" s="19">
         <f>IF(A50="","",IF(C50&lt;&gt;"",C50,$B$8*B50))</f>
         <v/>
       </c>
       <c r="E50" s="9" t="n"/>
-      <c r="F50" s="18">
+      <c r="F50" s="19">
         <f>IF(A50="","",D50-N(E50))</f>
         <v/>
       </c>
@@ -9668,14 +9659,14 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
-      <c r="B51" s="22" t="n"/>
+      <c r="B51" s="23" t="n"/>
       <c r="C51" s="9" t="n"/>
-      <c r="D51" s="18">
+      <c r="D51" s="19">
         <f>IF(A51="","",IF(C51&lt;&gt;"",C51,$B$8*B51))</f>
         <v/>
       </c>
       <c r="E51" s="9" t="n"/>
-      <c r="F51" s="18">
+      <c r="F51" s="19">
         <f>IF(A51="","",D51-N(E51))</f>
         <v/>
       </c>
@@ -9684,14 +9675,14 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
-      <c r="B52" s="22" t="n"/>
+      <c r="B52" s="23" t="n"/>
       <c r="C52" s="9" t="n"/>
-      <c r="D52" s="18">
+      <c r="D52" s="19">
         <f>IF(A52="","",IF(C52&lt;&gt;"",C52,$B$8*B52))</f>
         <v/>
       </c>
       <c r="E52" s="9" t="n"/>
-      <c r="F52" s="18">
+      <c r="F52" s="19">
         <f>IF(A52="","",D52-N(E52))</f>
         <v/>
       </c>
@@ -9700,14 +9691,14 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
-      <c r="B53" s="22" t="n"/>
+      <c r="B53" s="23" t="n"/>
       <c r="C53" s="9" t="n"/>
-      <c r="D53" s="18">
+      <c r="D53" s="19">
         <f>IF(A53="","",IF(C53&lt;&gt;"",C53,$B$8*B53))</f>
         <v/>
       </c>
       <c r="E53" s="9" t="n"/>
-      <c r="F53" s="18">
+      <c r="F53" s="19">
         <f>IF(A53="","",D53-N(E53))</f>
         <v/>
       </c>
@@ -9716,14 +9707,14 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
-      <c r="B54" s="22" t="n"/>
+      <c r="B54" s="23" t="n"/>
       <c r="C54" s="9" t="n"/>
-      <c r="D54" s="18">
+      <c r="D54" s="19">
         <f>IF(A54="","",IF(C54&lt;&gt;"",C54,$B$8*B54))</f>
         <v/>
       </c>
       <c r="E54" s="9" t="n"/>
-      <c r="F54" s="18">
+      <c r="F54" s="19">
         <f>IF(A54="","",D54-N(E54))</f>
         <v/>
       </c>
@@ -9732,14 +9723,14 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
-      <c r="B55" s="22" t="n"/>
+      <c r="B55" s="23" t="n"/>
       <c r="C55" s="9" t="n"/>
-      <c r="D55" s="18">
+      <c r="D55" s="19">
         <f>IF(A55="","",IF(C55&lt;&gt;"",C55,$B$8*B55))</f>
         <v/>
       </c>
       <c r="E55" s="9" t="n"/>
-      <c r="F55" s="18">
+      <c r="F55" s="19">
         <f>IF(A55="","",D55-N(E55))</f>
         <v/>
       </c>
@@ -9748,14 +9739,14 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
-      <c r="B56" s="22" t="n"/>
+      <c r="B56" s="23" t="n"/>
       <c r="C56" s="9" t="n"/>
-      <c r="D56" s="18">
+      <c r="D56" s="19">
         <f>IF(A56="","",IF(C56&lt;&gt;"",C56,$B$8*B56))</f>
         <v/>
       </c>
       <c r="E56" s="9" t="n"/>
-      <c r="F56" s="18">
+      <c r="F56" s="19">
         <f>IF(A56="","",D56-N(E56))</f>
         <v/>
       </c>
@@ -9764,14 +9755,14 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
-      <c r="B57" s="22" t="n"/>
+      <c r="B57" s="23" t="n"/>
       <c r="C57" s="9" t="n"/>
-      <c r="D57" s="18">
+      <c r="D57" s="19">
         <f>IF(A57="","",IF(C57&lt;&gt;"",C57,$B$8*B57))</f>
         <v/>
       </c>
       <c r="E57" s="9" t="n"/>
-      <c r="F57" s="18">
+      <c r="F57" s="19">
         <f>IF(A57="","",D57-N(E57))</f>
         <v/>
       </c>
@@ -9780,14 +9771,14 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="22" t="n"/>
+      <c r="B58" s="23" t="n"/>
       <c r="C58" s="9" t="n"/>
-      <c r="D58" s="18">
+      <c r="D58" s="19">
         <f>IF(A58="","",IF(C58&lt;&gt;"",C58,$B$8*B58))</f>
         <v/>
       </c>
       <c r="E58" s="9" t="n"/>
-      <c r="F58" s="18">
+      <c r="F58" s="19">
         <f>IF(A58="","",D58-N(E58))</f>
         <v/>
       </c>
@@ -9796,14 +9787,14 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
-      <c r="B59" s="22" t="n"/>
+      <c r="B59" s="23" t="n"/>
       <c r="C59" s="9" t="n"/>
-      <c r="D59" s="18">
+      <c r="D59" s="19">
         <f>IF(A59="","",IF(C59&lt;&gt;"",C59,$B$8*B59))</f>
         <v/>
       </c>
       <c r="E59" s="9" t="n"/>
-      <c r="F59" s="18">
+      <c r="F59" s="19">
         <f>IF(A59="","",D59-N(E59))</f>
         <v/>
       </c>
@@ -9812,14 +9803,14 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
-      <c r="B60" s="22" t="n"/>
+      <c r="B60" s="23" t="n"/>
       <c r="C60" s="9" t="n"/>
-      <c r="D60" s="18">
+      <c r="D60" s="19">
         <f>IF(A60="","",IF(C60&lt;&gt;"",C60,$B$8*B60))</f>
         <v/>
       </c>
       <c r="E60" s="9" t="n"/>
-      <c r="F60" s="18">
+      <c r="F60" s="19">
         <f>IF(A60="","",D60-N(E60))</f>
         <v/>
       </c>
@@ -9828,14 +9819,14 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
-      <c r="B61" s="22" t="n"/>
+      <c r="B61" s="23" t="n"/>
       <c r="C61" s="9" t="n"/>
-      <c r="D61" s="18">
+      <c r="D61" s="19">
         <f>IF(A61="","",IF(C61&lt;&gt;"",C61,$B$8*B61))</f>
         <v/>
       </c>
       <c r="E61" s="9" t="n"/>
-      <c r="F61" s="18">
+      <c r="F61" s="19">
         <f>IF(A61="","",D61-N(E61))</f>
         <v/>
       </c>
@@ -9844,14 +9835,14 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
-      <c r="B62" s="22" t="n"/>
+      <c r="B62" s="23" t="n"/>
       <c r="C62" s="9" t="n"/>
-      <c r="D62" s="18">
+      <c r="D62" s="19">
         <f>IF(A62="","",IF(C62&lt;&gt;"",C62,$B$8*B62))</f>
         <v/>
       </c>
       <c r="E62" s="9" t="n"/>
-      <c r="F62" s="18">
+      <c r="F62" s="19">
         <f>IF(A62="","",D62-N(E62))</f>
         <v/>
       </c>
@@ -9869,12 +9860,12 @@
       <c r="H63" s="2" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Total distributed per Ledger (category 'distribution')</t>
         </is>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"distribution",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
@@ -9886,12 +9877,12 @@
       <c r="H64" s="2" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Total 'Paid so far' entered above</t>
         </is>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="13">
         <f>SUM($E$13:$E$62)</f>
         <v/>
       </c>
@@ -9908,7 +9899,7 @@
           <t>Difference (should be zero)</t>
         </is>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="14">
         <f>B64-B65</f>
         <v/>
       </c>
@@ -9982,49 +9973,49 @@
       <c r="C4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Estate of</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>'Start here'!B20</f>
+      <c r="B5" s="11">
+        <f>IF('Start here'!B20="","",'Start here'!B20)</f>
         <v/>
       </c>
       <c r="C5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Date of death</t>
         </is>
       </c>
-      <c r="B6" s="23">
-        <f>'Start here'!B21</f>
+      <c r="B6" s="24">
+        <f>IF('Start here'!B21="","",'Start here'!B21)</f>
         <v/>
       </c>
       <c r="C6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Court and case number</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>'Start here'!B23</f>
+      <c r="B7" s="11">
+        <f>IF('Start here'!B23="","",'Start here'!B23)</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Personal representative</t>
         </is>
       </c>
-      <c r="B8" s="5">
-        <f>'Start here'!B24</f>
+      <c r="B8" s="11">
+        <f>IF('Start here'!B24="","",'Start here'!B24)</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -10035,57 +10026,57 @@
       <c r="C9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>I. Inventory at date of death</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Probate estate (Inventory, C)</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <f>Inventory!F8</f>
         <v/>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Non-probate: beneficiary designations (A)</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <f>Inventory!F6</f>
         <v/>
       </c>
       <c r="C12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Non-probate: joint and trust (B)</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <f>Inventory!F7</f>
         <v/>
       </c>
       <c r="C13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Total assets at date of death</t>
         </is>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
@@ -10097,81 +10088,81 @@
       <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>II. Receipts into the estate account</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Transfers of inventory assets into the estate account</t>
         </is>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"transfer in",Ledger!$D$13:$D$212)</f>
         <v/>
       </c>
       <c r="C17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Proceeds of sales</t>
         </is>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"sale proceeds",Ledger!$D$13:$D$212)</f>
         <v/>
       </c>
       <c r="C18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Income: interest</t>
         </is>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"income-interest",Ledger!$D$13:$D$212)</f>
         <v/>
       </c>
       <c r="C19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Income: dividends</t>
         </is>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"income-dividend",Ledger!$D$13:$D$212)</f>
         <v/>
       </c>
       <c r="C20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Income: other</t>
         </is>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"income-other",Ledger!$D$13:$D$212)</f>
         <v/>
       </c>
       <c r="C21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Total receipts</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>SUM(B17:B21)</f>
         <v/>
       </c>
@@ -10183,105 +10174,105 @@
       <c r="C23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>III. Disbursements</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Funeral</t>
         </is>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"funeral",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"administration",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"legal",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"accounting",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"tax",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Debts and claims paid</t>
         </is>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"debt paid",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Reimbursement to executor</t>
         </is>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"reimbursement to executor",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
       <c r="C31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Total disbursements before distributions</t>
         </is>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="28">
         <f>SUM(B25:B31)</f>
         <v/>
       </c>
@@ -10293,21 +10284,21 @@
       <c r="C33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>IV. Distributions to beneficiaries</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Distributions paid (Ledger)</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="13">
         <f>SUMIF(Ledger!$C$13:$C$212,"distribution",Ledger!$E$13:$E$212)</f>
         <v/>
       </c>
@@ -10319,81 +10310,81 @@
       <c r="C36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>V. Reconciliation</t>
         </is>
       </c>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25" t="n"/>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total receipts (II)</t>
         </is>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="13">
         <f>B22</f>
         <v/>
       </c>
       <c r="C38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Less total disbursements (III)</t>
         </is>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="13">
         <f>B32</f>
         <v/>
       </c>
       <c r="C39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Less distributions (IV)</t>
         </is>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="13">
         <f>B35</f>
         <v/>
       </c>
       <c r="C40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Balance remaining in estate account</t>
         </is>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="28">
         <f>B38-B39-B40</f>
         <v/>
       </c>
       <c r="C41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Ledger running balance (should match)</t>
         </is>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="13">
         <f>Ledger!B7</f>
         <v/>
       </c>
       <c r="C42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Difference (should be zero)</t>
         </is>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="28">
         <f>B41-B42</f>
         <v/>
       </c>
@@ -10405,69 +10396,69 @@
       <c r="C44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>VI. Still to do</t>
         </is>
       </c>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="26" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Assets in inventory not yet valued (count)</t>
         </is>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="29">
         <f>Inventory!F10</f>
         <v/>
       </c>
       <c r="C46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Claims still pending (count)</t>
         </is>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="29">
         <f>Claims!B9</f>
         <v/>
       </c>
       <c r="C47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Outgoing ledger rows without a receipt (count)</t>
         </is>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="29">
         <f>Ledger!B8</f>
         <v/>
       </c>
       <c r="C48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Reserve held for taxes and final costs</t>
         </is>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="13">
         <f>'Start here'!B26</f>
         <v/>
       </c>
       <c r="C49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Available for distribution after reserve and specific gifts</t>
         </is>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="13">
         <f>Distribution!B8</f>
         <v/>
       </c>
